--- a/Kif13a_sonuclar.xlsx
+++ b/Kif13a_sonuclar.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tum Beyin Siralamasi" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolgesel Heterojenlik" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kohort Tekrari" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tespit vs Seviye" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Yaslanma Donor Listesi'!$A$4:$I$198</definedName>
@@ -27,7 +28,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="+0.000;-0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -35,6 +36,8 @@
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
     <numFmt numFmtId="170" formatCode="+0.000"/>
+    <numFmt numFmtId="171" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -88,7 +91,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +111,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +180,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -571,7 +581,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Kif13a oligodendrosit soyuna spesifik, genel bir glia geni degil.</t>
+          <t>Olgun oligodendrosit siralamada birinci, ama aradaki farkin buyuk kismi tespit orani etkisi.</t>
         </is>
       </c>
     </row>
@@ -579,7 +589,7 @@
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Olgun oligodendrosit 265 alt sinif icinde birinci. Astrosit ve mikroglia yaklasik 16 kat dusuk.</t>
+          <t>265 alt sinif icinde oligodendrosit her olcutte birinci, onculu ikinci.</t>
         </is>
       </c>
     </row>
@@ -587,31 +597,31 @@
       <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ayrinti: Tum Beyin Siralamasi sayfasi.</t>
+          <t>Havuzlanmis ortalamalardan kat farki OKUNAMAZ. Astrositle arasindaki fark 16 kat degil, kabaca 1,8 kat tespit orani ve 2,0 kat seviye.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Ayrinti: Tum Beyin Siralamasi ve Tespit vs Seviye sayfalari.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Bulgu 2</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Oncul hucreler bolgesel olarak degisken, olgun hucreler duz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>OPC yayilimi oligodendrositin yaklasik uc kati. Korteks ve hipokampusta yuksek, serebellum ve medullada dusuk.</t>
         </is>
       </c>
     </row>
@@ -619,7 +629,7 @@
       <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Varyans farki anlamli (Levene p &lt; 0.0001) ve bagimsiz kohortta tekrarlaniyor (Spearman rho = +0.96).</t>
+          <t>OPC yayilimi oligodendrositin yaklasik uc kati. Korteks ve hipokampusta yuksek, serebellum ve medullada dusuk.</t>
         </is>
       </c>
     </row>
@@ -627,31 +637,31 @@
       <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ayrinti: Bolgesel Heterojenlik ve Kohort Tekrari sayfalari.</t>
+          <t>Varyans farki anlamli (Levene p &lt; 0.0001) ve bagimsiz kohortta tekrarlaniyor (Spearman rho = +0.96).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ayrinti: Bolgesel Heterojenlik ve Kohort Tekrari sayfalari.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Bulgu 3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Yaslanmayla artis sadece olgun oligodendrositte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>53 genc fare (yaklasik 2 aylik) ile 44 yasli fare (yaklasik 18 aylik) karsilastirildi.</t>
         </is>
       </c>
     </row>
@@ -659,7 +669,7 @@
       <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Her fare tek bir gozlem sayildi, boylece ayni hayvandan gelen binlerce hucre yalanci tekrar olusturmadi.</t>
+          <t>53 genc fare (yaklasik 2 aylik) ile 44 yasli fare (yaklasik 18 aylik) karsilastirildi.</t>
         </is>
       </c>
     </row>
@@ -667,159 +677,168 @@
       <c r="A16" s="3" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Her fare tek bir gozlem sayildi, boylece ayni hayvandan gelen binlerce hucre yalanci tekrar olusturmadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Ayrinti: Yaslanma Donor Testi sayfasi.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Ana sayisal sonuc</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Hucre tipi</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Genc ortalama (log2)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Yasli ortalama (log2)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Fark (log2)</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Kat degisim</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Mann-Whitney p</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Cliff delta</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Olgun oligodendrosit</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>7.867824</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>8.117736000000001</v>
-      </c>
-      <c r="D20" s="9">
-        <f>C20-B20</f>
-        <v>0.24991200000000102</v>
-      </c>
-      <c r="E20" s="8">
-        <f>POWER(2,D20)</f>
-        <v>1.1891345792057955</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0.000242</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0.43482</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>OPC (oncul)</t>
+          <t>Olgun oligodendrosit</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>6.792572</v>
+        <v>7.867824</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>6.923194</v>
+        <v>8.117736000000001</v>
       </c>
       <c r="D21" s="9">
         <f>C21-B21</f>
-        <v>0.1306219999999998</v>
+        <v>0.24991200000000102</v>
       </c>
       <c r="E21" s="8">
         <f>POWER(2,D21)</f>
+        <v>1.1891345792057955</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.000242</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.43482</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>OPC (oncul)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>6.792572</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>6.923194</v>
+      </c>
+      <c r="D22" s="9">
+        <f>C22-B22</f>
+        <v>0.1306219999999998</v>
+      </c>
+      <c r="E22" s="8">
+        <f>POWER(2,D22)</f>
         <v>1.094765594080088</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F22" s="11" t="n">
         <v>0.219357</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G22" s="9" t="n">
         <v>0.145798</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Notlar</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>- Olcum birimi log2(CPM + 1). Olculen sey mRNA'dir, protein degildir.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>- Fark ve kat degisim sutunlari canli formuldur. p degerleri ve Cliff delta scipy ile hesaplandi, deger olarak yazildi.</t>
+          <t>- Olcum birimi log2(CPM + 1). Olculen sey mRNA'dir, protein degildir.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>- Kif13a, Allen'in yayimlanmis yasa bagli farkli ifade tablosunda yer almiyor, yani etki gercek ama mutevazi.</t>
+          <t>- Fark ve kat degisim sutunlari canli formuldur. p degerleri ve Cliff delta scipy ile hesaplandi, deger olarak yazildi.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>- Yaslanma kohortu 13 bolgenin sadece 7'sini kapsiyor. Serebellum, medulla, talamus, olfaktor ve CTXsp disarida.</t>
+          <t>- Kif13a, Allen'in yayimlanmis yasa bagli farkli ifade tablosunda yer almiyor, yani etki gercek ama mutevazi.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
+          <t>- Yaslanma kohortu 13 bolgenin sadece 7'sini kapsiyor. Serebellum, medulla, talamus, olfaktor ve CTXsp disarida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
           <t>- Kaynak kod: github.com/ikoshos-gland/kif13a-allenbrain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="A1:G1"/>
@@ -833,6 +852,492 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B11:G11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tespit orani mi, ifade seviyesi mi?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Siralamadaki buyuk farkin ne kadari geni kac hucrenin gosterdiginden, ne kadari seviyeden geliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Alt sinif</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Genel sira</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Hucre</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Ortalama (log2, sifirlar dahil)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Tespit orani</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Tespit edilende seviye (CPM)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>YANILTICI kat</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Tespit orani kati</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Seviye kati</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>327 Oligo NN</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>371211</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>7.765019914220215</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.9250264674268812</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>335.4797636443221</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>326 OPC NN</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>106459</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>6.764457360101072</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.850797020449187</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>246.4048478492157</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>2.000780017670547</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>1.087246952203129</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>1.361498227703761</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>332 SMC NN</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>121</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>13705</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>4.424467163531558</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.569500182415177</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>217.1286634284079</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>10.12993316644151</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>1.624277736846304</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>1.545073590686644</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>335 BAM NN</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>5516</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>4.139340412146483</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.5398839738941261</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>202.2473290800229</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>12.34349895999417</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>1.713380118981423</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>1.658759921183351</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>318 Astro-NT NN</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>139030</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>4.086697386960369</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.5374955045673596</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>193.4454302475901</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>12.80222378399456</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>1.720993867979329</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>1.734234627382734</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>334 Microglia NN</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>168</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>81472</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>3.879017706744648</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0.4917272191673212</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>235.9692420590459</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>14.78438378079829</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>1.88117808282669</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>1.421709714015931</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>333 Endo NN</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>84356</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>3.790201947700223</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0.4937763763099246</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>203.4987653894541</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>15.72314556804754</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>1.873371250240366</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>1.648559208712073</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>319 Astro-TE NN</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>178</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>144668</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3.772723433937706</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0.5096496806481047</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>168.1995320023066</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>15.9147929238524</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>1.815024128437706</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>1.994534465409342</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>316 Bergmann NN</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>190</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>3321</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>3.606476154080097</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.5323697681421259</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>108.4692575159436</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>17.85855888344941</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>1.73756385651848</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>3.09285572084801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>330 VLMC NN</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>205</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>8544</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>3.433970357876873</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.4590355805243445</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>177.6307951743404</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>20.12685089160359</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>2.015151998392472</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>1.888635150876044</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>331 Peri NN</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>240</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>23170</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>2.85009551456625</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0.3519205869659041</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>273.1248607492214</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>30.1675242643276</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>2.628509105994707</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>1.228301820361765</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Notlar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>- Kesin ozdeslik: ortalama(tum hucreler) = tespit orani x ortalama(tespit edilen hucreler). Tespit edilmeyen hucre log2 olceginde tam olarak 0 katkı verir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>- Bu yuzden iki ortalamanin farkindan 2 ussu alarak kat degisim hesaplanamaz. Logaritmanin ortalamasi, ortalamanin logaritmasi degildir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>- YANILTICI kat sutunu kirmizi: bu sutun yanlis yorumun ne kadar sismis oldugunu gostermek icin duruyor, kullanilmamali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>- Oligodendrosit ile telensefalik astrosit arasindaki gercek fark: tespit oraninda 1,82 kat, tespit edilen hucrelerdeki seviyede 1,99 kat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>- Perisit uyarisi: genel siralamada 240. sirada ama tespit edilen perisitlerde seviye 273 CPM, astrositin 168 CPM degerinin uzerinde. Perisitler az RNA tasir, dolayisiyla dusuk sirasi buyuk olasilikla teknik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>- 10x verisinde tespit orani hucrenin RNA icerigini takip eder. Bu bilinen bir teknik karistirici ve bu analizde duzeltilmedi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10426,7 +10931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -18916,27 +19421,35 @@
     <row r="273">
       <c r="A273" s="12" t="inlineStr">
         <is>
-          <t>- Astrosit, mikroglia ve endotel 3,7 ile 3,9 arasinda, yani oligodendrositin yaklasik onaltida biri. Kif13a genel bir glia geni degil.</t>
+          <t>- DIKKAT: Ortalama sutunu sifirlari da iceriyor, cunku tespit edilmeyen hucre log2(CPM+1) olceginde tam olarak 0 verir. Bu yuzden iki ortalamanin farkindan kat degisim OKUNAMAZ.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="12" t="inlineStr">
         <is>
-          <t>- En dusuk degerler olfaktor bulbusun inhibitor internoronlarinda.</t>
+          <t>- Astrosit, mikroglia ve endotel 3,7 ile 3,9 arasinda gorunuyor ama bunun buyuk kismi dusuk tespit orani. Ayrinti icin Tespit vs Seviye sayfasina bakin.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="12" t="inlineStr">
         <is>
+          <t>- En dusuk degerler olfaktor bulbusun inhibitor internoronlarinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="inlineStr">
+        <is>
           <t>- Ortancalar parca ortancalarindan havuzlanamaz, bu yuzden siralama ortalama uzerinden. Hucreler havuzlanmis, donor duzeyi duzeltmesi yok, siralama betimseldir.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H269"/>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A276:H276"/>
     <mergeCell ref="A272:H272"/>
     <mergeCell ref="A275:H275"/>
     <mergeCell ref="A2:H2"/>

--- a/Kif13a_sonuclar.xlsx
+++ b/Kif13a_sonuclar.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaslanma sonucu" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaslanma donorler" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolgesel 13 parca" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaslanma bolge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kohort tekrari" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tum beyin siralamasi" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tespit vs seviye" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veri seti" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Özet tablolar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaşlanma sonucu" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaşlanma donörler" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bölgesel 13 parça" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yaşlanma bölge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kohort tekrarı" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tüm beyin sıralaması" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tespit vs seviye" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veri seti" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,12 +88,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -460,6 +461,586 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>En yüksek 10 hücre tipi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alt sınıf</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sınıf</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Hücre</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Ortalama (log2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Oligo (olgun oligodendrosit)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>OPC-Oligo</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>371211</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7.765019914220215</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>OPC (öncül)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>OPC-Oligo</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>106459</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.764457360101072</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>MH Tac2 Glut</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Medial habenula</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4662</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.757697807872158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>PRP Gata3 Slc6a5</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Medulla GABA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>716</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.679214888268157</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>NTS Dbh Glut</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Medulla</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1725</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.041827412289855</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>MV Pax6</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Medulla GABA</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>623</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.679213168218299</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>MV Nkx6-1</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Medulla GABA</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1271</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.667426185680566</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>MV-SPIV-PRP Dmbx1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Medulla GABA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>875</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.661107027771428</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PRP Otp</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Medulla GABA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2312</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.643603335640138</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>VMH Nr5a1 Glut</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Hipotalamus</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>3793</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.596371214025836</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Glia tipleri karşılaştırması</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Hücre tipi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Ortalama (log2)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>İfade eden oran</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Olgun oligodendrosit</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7.765019914220215</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.9250264674268812</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>OPC</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>6.764457360101072</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.850797020449187</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Astrosit (telensefalik)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3.772723433937706</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.5096496806481047</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Mikroglia</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3.879017706744648</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.4917272191673212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Endotel</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3.790201947700223</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.4937763763099246</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Perisit</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2.85009551456625</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.3519205869659041</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>En düşük hücreler</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Alt sınıf</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Ortalama (log2)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>İfade eden oran</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>OB Trdn Gaba</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.656512470708872</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.09451627284886301</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>OB-out Frmd7 Gaba</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0.7941136664323259</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.1127901883486639</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>OB-STR-CTX Inh IMN</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1.203411173657884</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.1743668066692121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>OB-in Frmd7 Gaba</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1.267535100730406</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.1935426169394508</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sncg Gaba (korteks)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1.978274600239391</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.3862894450489662</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Vip Gaba (korteks)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2.217751568167665</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0.3680239520958083</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Genç ve yaşlı farelerde Kif13a, donör düzeyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Hücre tipi</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Genç ortalama (log2)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Yaşlı ortalama (log2)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Fark (log2)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Kat değişim</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Mann-Whitney p</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Welch t p</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Cliff delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Olgun oligodendrosit</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7.867824467924529</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>8.117736459090908</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.2499119911663792</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1.189134571924724</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.0002423364789209</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>0.0043761078733528</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0.434819897084048</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>OPC (öncül)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>6.792571864150944</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>6.923193772727274</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0.1306219085763293</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1.09476552470473</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0.2193571229458359</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>0.2405674806528518</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0.1457975986277873</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -476,24 +1057,24 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Genc ve yasli farelerde Kif13a, donor duzeyi</t>
+          <t>Genç ve yaşlı farelerde Kif13a, donör düzeyi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hucre tipi</t>
+          <t>Hücre tipi</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Genc ortalama (log2)</t>
+          <t>Genç ortalama (log2)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yasli ortalama (log2)</t>
+          <t>Yaşlı ortalama (log2)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -503,7 +1084,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kat degisim</t>
+          <t>Kat değişim</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -528,53 +1109,53 @@
           <t>Olgun oligodendrosit</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>7.867824467924529</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>8.117736459090908</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="7" t="n">
         <v>0.2499119911663792</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>1.189134571924724</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="8" t="n">
         <v>0.0002423364789209</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="8" t="n">
         <v>0.0043761078733528</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="7" t="n">
         <v>0.434819897084048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>OPC (oncul)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+          <t>OPC (öncül)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>6.792571864150944</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>6.923193772727274</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="7" t="n">
         <v>0.1306219085763293</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.09476552470473</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="8" t="n">
         <v>0.2193571229458359</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="8" t="n">
         <v>0.2405674806528518</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="7" t="n">
         <v>0.1457975986277873</v>
       </c>
     </row>
@@ -582,14 +1163,14 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>log2 degerlerinin CPM karsiligi (ortanca uzerinden)</t>
+          <t>log2 değerlerinin CPM karşılığı (ortanca üzerinden)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Olcum</t>
+          <t>Ölçüm</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -599,59 +1180,59 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CPM karsiligi</t>
+          <t>CPM karşılığı</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Oligodendrosit, genc</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
+          <t>Oligodendrosit, genç</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>8.456</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="4" t="n">
         <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Oligodendrosit, yasli</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+          <t>Oligodendrosit, yaşlı</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>8.717000000000001</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="4" t="n">
         <v>420</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>OPC, genc</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
+          <t>OPC, genç</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>7.83</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="4" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>OPC, yasli</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
+          <t>OPC, yaşlı</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>7.808</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="4" t="n">
         <v>223</v>
       </c>
     </row>
@@ -659,24 +1240,24 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Hucreler havuzlanmis ozet</t>
+          <t>Hücreler havuzlanmış özet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Yas grubu</t>
+          <t>Yaş grubu</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -696,14 +1277,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Ifade eden oran</t>
+          <t>İfade eden oran</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -711,26 +1292,26 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="4" t="n">
         <v>33243</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>6.9350824</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>7.8295636</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="9" t="n">
         <v>0.8714315795806636</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -738,26 +1319,26 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="4" t="n">
         <v>83475</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>7.9478726</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>8.456071</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.946451033243486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -765,26 +1346,26 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="4" t="n">
         <v>54927</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>6.969838</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>7.8079867</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>0.879494601926193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -792,19 +1373,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="4" t="n">
         <v>81823</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>8.226858</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>8.717043</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.9499651687178422</v>
       </c>
     </row>
@@ -813,7 +1394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -834,7 +1415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gruplarin ozeti</t>
+          <t>Grupların özeti</t>
         </is>
       </c>
     </row>
@@ -846,27 +1427,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fare sayisi</t>
+          <t>Fare sayısı</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>En kucuk yas (gun)</t>
+          <t>En küçük yaş (gün)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>En buyuk yas (gun)</t>
+          <t>En büyük yaş (gün)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ortanca yas (gun)</t>
+          <t>Ortanca yaş (gün)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Disi</t>
+          <t>Dişi</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -878,7 +1459,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Genc yetiskin</t>
+          <t>Genç yetişkin</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -903,7 +1484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Yasli</t>
+          <t>Yaşlı</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -929,19 +1510,19 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Genc yetiskin grubu, yasa gore fare sayisi</t>
+          <t>Genç yetişkin grubu, yaşa göre fare sayısı</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Yas etiketi</t>
+          <t>Yaş etiketi</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>Gün</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -951,7 +1532,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Disi</t>
+          <t>Dişi</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1287,19 +1868,19 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Yasli grup, yasa gore fare sayisi</t>
+          <t>Yaşlı grup, yaşa göre fare sayısı</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Yas etiketi</t>
+          <t>Yaş etiketi</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>Gün</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1309,7 +1890,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Disi</t>
+          <t>Dişi</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1569,19 +2150,19 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Fare basina hucre katkisi</t>
+          <t>Fare başına hücre katkısı</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Yas grubu</t>
+          <t>Yaş grubu</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1591,12 +2172,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toplam hucre</t>
+          <t>Toplam hücre</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Fare basi ortanca</t>
+          <t>Fare başı ortanca</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1606,14 +2187,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>En cok</t>
+          <t>En çok</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1624,23 +2205,23 @@
       <c r="C44" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="4" t="n">
         <v>33243</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="4" t="n">
         <v>476</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="4" t="n">
         <v>2272</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1651,23 +2232,23 @@
       <c r="C45" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="4" t="n">
         <v>83475</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="4" t="n">
         <v>1347</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="4" t="n">
         <v>4127</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1678,23 +2259,23 @@
       <c r="C46" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="4" t="n">
         <v>54927</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="4" t="n">
         <v>1401.5</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="4" t="n">
         <v>2434</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1705,16 +2286,16 @@
       <c r="C47" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="4" t="n">
         <v>81823</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="4" t="n">
         <v>1432.5</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="4" t="n">
         <v>6830</v>
       </c>
     </row>
@@ -1723,7 +2304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1743,14 +2324,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>13 parcada OPC ve olgun oligodendrosit</t>
+          <t>13 parçada OPC ve olgun oligodendrosit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Parca</t>
+          <t>Parça</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1785,19 +2366,19 @@
           <t>HPF</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>7.382030965821408</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>7.893821003975312</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="7" t="n">
         <v>0.5117900381539036</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <v>0.914218763076408</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>0.934430581364481</v>
       </c>
     </row>
@@ -1807,19 +2388,19 @@
           <t>Isocortex-1</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>7.340097694326241</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>7.545079194591937</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="7" t="n">
         <v>0.2049815002656956</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>0.8973717146433041</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.902409046214356</v>
       </c>
     </row>
@@ -1829,19 +2410,19 @@
           <t>Isocortex-2</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>7.333758118274734</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>7.94648454471572</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="7" t="n">
         <v>0.612726426440986</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>0.8956118833469611</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.927637937555154</v>
       </c>
     </row>
@@ -1851,19 +2432,19 @@
           <t>CTXsp</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>7.304814283266312</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>7.845153407868265</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="7" t="n">
         <v>0.5403391246019531</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>0.9094564794396161</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.9341325616645996</v>
       </c>
     </row>
@@ -1873,19 +2454,19 @@
           <t>OLF</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>7.205257060149839</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>7.671045113812155</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="7" t="n">
         <v>0.4657880536623153</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>0.8797716732072779</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.922242684673624</v>
       </c>
     </row>
@@ -1895,19 +2476,19 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6.990709758841848</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>7.621401727281114</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.6306919684392662</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>0.8669830206865871</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>0.9064028046867793</v>
       </c>
     </row>
@@ -1917,19 +2498,19 @@
           <t>HY</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>6.74788675954767</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>7.946407543903154</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="7" t="n">
         <v>1.198520784355484</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>0.8594257854821236</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.939379509908062</v>
       </c>
     </row>
@@ -1939,19 +2520,19 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>6.415280829782344</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>7.924866840402514</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="7" t="n">
         <v>1.50958601062017</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="9" t="n">
         <v>0.8233067459780993</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.9338962605548854</v>
       </c>
     </row>
@@ -1961,19 +2542,19 @@
           <t>TH</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>6.319708257968599</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>7.888318779091632</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="7" t="n">
         <v>1.568610521123033</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>0.8133944699180214</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.9374871054260367</v>
       </c>
     </row>
@@ -1983,19 +2564,19 @@
           <t>PAL</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>6.259326344696382</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>7.368485617585351</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="7" t="n">
         <v>1.109159272888968</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <v>0.7869234353160429</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.8794931568656941</v>
       </c>
     </row>
@@ -2005,19 +2586,19 @@
           <t>P</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>6.197136568039017</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>7.540377059235904</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="7" t="n">
         <v>1.343240491196886</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>0.805548517861667</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.9113696704669686</v>
       </c>
     </row>
@@ -2027,19 +2608,19 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>5.951040082617001</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>7.742076409893479</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="7" t="n">
         <v>1.791036327276478</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <v>0.778414517669532</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.9409296320206584</v>
       </c>
     </row>
@@ -2049,19 +2630,19 @@
           <t>MY</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>5.7860686169066</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>7.738023811576183</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="7" t="n">
         <v>1.951955194669583</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>0.7560750892548659</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.932666240862962</v>
       </c>
     </row>
@@ -2069,14 +2650,14 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Yayilim karsilastirmasi</t>
+          <t>Yayılım karşılaştırması</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Olcut</t>
+          <t>Ölçüt</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2098,48 +2679,48 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>En dusuk</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
+          <t>En düşük</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
         <v>5.7860686169066</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>7.368485617585351</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="6" t="n">
         <v>0.7852452888145409</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>En yuksek</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
+          <t>En yüksek</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>7.382030965821408</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>7.94648454471572</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="6" t="n">
         <v>0.9289681398462337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Aralik</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
+          <t>Aralık</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
         <v>1.595962348914808</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>0.5779989271303698</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="6" t="n">
         <v>2.761185659700771</v>
       </c>
     </row>
@@ -2149,45 +2730,45 @@
           <t>Standart sapma</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>0.5810931625615068</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>0.1849826263769152</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="6" t="n">
         <v>3.141339129748804</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Degisim katsayisi (%)</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
+          <t>Değişim katsayısı (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>8.659797467780059</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>2.388732821335862</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="6" t="n">
         <v>3.62526833910927</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Ifade eden oran araligi</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
+          <t>İfade eden oran aralığı</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>0.1581436738215422</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>0.06143647515496431</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="6" t="n">
         <v>2.574100701946985</v>
       </c>
     </row>
@@ -2195,7 +2776,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Istatistik testleri</t>
+          <t>İstatistik testleri</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2788,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Istatistik</t>
+          <t>İstatistik</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2217,20 +2798,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>p degeri</t>
+          <t>p değeri</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Varyans orani (F testi)</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n">
+          <t>Varyans oranı (F testi)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="7" t="n"/>
       <c r="D28" s="10" t="n">
         <v>0.000372</v>
       </c>
@@ -2241,10 +2822,10 @@
           <t>Levene (Brown-Forsythe)</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="6" t="n">
         <v>24.95</v>
       </c>
-      <c r="C29" s="5" t="n"/>
+      <c r="C29" s="7" t="n"/>
       <c r="D29" s="10" t="n">
         <v>3e-05</v>
       </c>
@@ -2255,8 +2836,8 @@
           <t>Korteks+HPF vs arka beyin, OPC</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="5" t="n">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="7" t="n">
         <v>1.335</v>
       </c>
       <c r="D30" s="10" t="n">
@@ -2269,8 +2850,8 @@
           <t>Korteks+HPF vs arka beyin, Oligo</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="5" t="n">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="7" t="n">
         <v>0.107</v>
       </c>
       <c r="D31" s="10" t="n">
@@ -2282,7 +2863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2304,29 +2885,29 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Yaslanma kohortunun 7 bolgesi, yas grubuna gore</t>
+          <t>Yaşlanma kohortunun 7 bölgesi, yaş grubuna göre</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bolge</t>
+          <t>Bölge</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Yas grubu</t>
+          <t>Yaş grubu</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2346,7 +2927,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Ifade eden oran</t>
+          <t>İfade eden oran</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2939,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2366,19 +2947,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="4" t="n">
         <v>5909</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>7.4181957</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>8.106101000000001</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="9" t="n">
         <v>0.914198679979692</v>
       </c>
     </row>
@@ -2390,7 +2971,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2398,19 +2979,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="4" t="n">
         <v>11771</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>7.302477</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>8.025351000000001</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>0.9049358593152664</v>
       </c>
     </row>
@@ -2422,7 +3003,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2430,19 +3011,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="4" t="n">
         <v>1198</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>7.0475044</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>7.8208885</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.8948247078464107</v>
       </c>
     </row>
@@ -2454,7 +3035,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2462,19 +3043,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="4" t="n">
         <v>4238</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>7.1246595</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>7.8660803</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>0.8978291647003304</v>
       </c>
     </row>
@@ -2486,7 +3067,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2494,19 +3075,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="4" t="n">
         <v>5198</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>7.431852</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>8.116034000000001</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>0.911119661408234</v>
       </c>
     </row>
@@ -2518,7 +3099,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2526,19 +3107,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="4" t="n">
         <v>9763</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>7.244474</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>8.002133000000001</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>0.8957287718938851</v>
       </c>
     </row>
@@ -2550,7 +3131,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2558,19 +3139,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="4" t="n">
         <v>6064</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>6.5772257</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>7.61125</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.845811345646438</v>
       </c>
     </row>
@@ -2582,7 +3163,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2590,19 +3171,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="4" t="n">
         <v>8730</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>6.6555014</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>7.577699</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="9" t="n">
         <v>0.8591065292096219</v>
       </c>
     </row>
@@ -2614,7 +3195,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2622,19 +3203,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="4" t="n">
         <v>3168</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>6.0950522</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>7.387064</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="9" t="n">
         <v>0.7935606060606061</v>
       </c>
     </row>
@@ -2646,7 +3227,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2654,19 +3235,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="4" t="n">
         <v>9384</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>6.3697906</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>7.448126</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <v>0.8274722932651322</v>
       </c>
     </row>
@@ -2678,7 +3259,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2686,19 +3267,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="4" t="n">
         <v>5022</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>6.498734</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>7.6054444</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>0.8295499800876145</v>
       </c>
     </row>
@@ -2710,7 +3291,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2718,19 +3299,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="4" t="n">
         <v>3150</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>6.9180202</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>7.7828946</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="9" t="n">
         <v>0.8784126984126984</v>
       </c>
     </row>
@@ -2742,7 +3323,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2750,19 +3331,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="4" t="n">
         <v>6684</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>7.1521654</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>7.9652705</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="9" t="n">
         <v>0.8901855176540994</v>
       </c>
     </row>
@@ -2774,7 +3355,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2782,19 +3363,19 @@
           <t>326 OPC NN</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="4" t="n">
         <v>7891</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>7.132727</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>7.8606396</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="9" t="n">
         <v>0.896464326447852</v>
       </c>
     </row>
@@ -2806,7 +3387,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2814,19 +3395,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="4" t="n">
         <v>6966</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>7.948546</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>8.568778</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>0.9358311800172264</v>
       </c>
     </row>
@@ -2838,7 +3419,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2846,19 +3427,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="4" t="n">
         <v>8388</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>8.312139500000001</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>8.865266999999999</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="9" t="n">
         <v>0.9422985216976634</v>
       </c>
     </row>
@@ -2870,7 +3451,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2878,19 +3459,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="4" t="n">
         <v>2070</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>8.044663999999999</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>8.522266</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>0.9497584541062802</v>
       </c>
     </row>
@@ -2902,7 +3483,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2910,19 +3491,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="4" t="n">
         <v>4908</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>8.326701999999999</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>8.779783</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>0.95680521597392</v>
       </c>
     </row>
@@ -2934,7 +3515,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2942,19 +3523,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="4" t="n">
         <v>6452</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>8.007250000000001</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>8.647285</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>0.935368877867328</v>
       </c>
     </row>
@@ -2966,7 +3547,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2974,19 +3555,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="4" t="n">
         <v>15692</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>8.306156</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="5" t="n">
         <v>8.903229</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>0.9346163650267652</v>
       </c>
     </row>
@@ -2998,7 +3579,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3006,19 +3587,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="4" t="n">
         <v>21472</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>8.139359000000001</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>8.586646999999999</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>0.9575260804769</v>
       </c>
     </row>
@@ -3030,7 +3611,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3038,19 +3619,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="4" t="n">
         <v>15331</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>8.19346</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>8.62269</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>0.9577326984541126</v>
       </c>
     </row>
@@ -3062,7 +3643,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3070,19 +3651,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="4" t="n">
         <v>18198</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>7.9330397</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>8.387382499999999</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="9" t="n">
         <v>0.9524123530058248</v>
       </c>
     </row>
@@ -3094,7 +3675,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3102,19 +3683,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="4" t="n">
         <v>21906</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="5" t="n">
         <v>8.185214999999999</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="5" t="n">
         <v>8.61558</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="9" t="n">
         <v>0.9589153656532456</v>
       </c>
     </row>
@@ -3126,7 +3707,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3134,19 +3715,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="4" t="n">
         <v>18498</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>7.7508726</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="5" t="n">
         <v>8.299305</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="9" t="n">
         <v>0.9381554762677046</v>
       </c>
     </row>
@@ -3158,7 +3739,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3166,19 +3747,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="4" t="n">
         <v>4212</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>7.992005</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="5" t="n">
         <v>8.526125</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="9" t="n">
         <v>0.9449192782526116</v>
       </c>
     </row>
@@ -3190,7 +3771,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>genç</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3198,19 +3779,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="4" t="n">
         <v>9819</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="5" t="n">
         <v>7.8678527</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="5" t="n">
         <v>8.416407</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="9" t="n">
         <v>0.9409308483552296</v>
       </c>
     </row>
@@ -3222,7 +3803,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>aged</t>
+          <t>yaşlı</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3230,19 +3811,19 @@
           <t>327 Oligo NN</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="4" t="n">
         <v>11386</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>8.223668</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="5" t="n">
         <v>8.725830999999999</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.9480063235552432</v>
       </c>
     </row>
@@ -3251,7 +3832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3276,7 +3857,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bolge</t>
+          <t>Bölge</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3286,7 +3867,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yaslanma kohortu (log2)</t>
+          <t>Yaşlanma kohortu (log2)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3301,13 +3882,13 @@
           <t>HPF</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>7.382030965821408</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>7.4181957</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="7" t="n">
         <v>0.03616473417859201</v>
       </c>
     </row>
@@ -3317,13 +3898,13 @@
           <t>Isocortex</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>7.334648176483336</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>7.431852</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="7" t="n">
         <v>0.09720382351666412</v>
       </c>
     </row>
@@ -3333,13 +3914,13 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>6.990709758841848</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>7.1521654</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="7" t="n">
         <v>0.1614556411581525</v>
       </c>
     </row>
@@ -3349,13 +3930,13 @@
           <t>HY</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>6.74788675954767</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>7.0475044</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="7" t="n">
         <v>0.2996176404523299</v>
       </c>
     </row>
@@ -3365,13 +3946,13 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>6.415280829782344</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>6.5772257</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="7" t="n">
         <v>0.1619448702176554</v>
       </c>
     </row>
@@ -3381,13 +3962,13 @@
           <t>PAL</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6.259326344696382</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>6.498734</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.2394076553036175</v>
       </c>
     </row>
@@ -3397,13 +3978,13 @@
           <t>P</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>6.197136568039017</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>6.0950522</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="7" t="n">
         <v>-0.1020843680390175</v>
       </c>
     </row>
@@ -3418,7 +3999,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Bolge</t>
+          <t>Bölge</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3428,7 +4009,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Yaslanma kohortu (log2)</t>
+          <t>Yaşlanma kohortu (log2)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3443,13 +4024,13 @@
           <t>HY</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>7.946407543903154</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>8.044663999999999</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="7" t="n">
         <v>0.09825645609684486</v>
       </c>
     </row>
@@ -3459,13 +4040,13 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>7.924866840402514</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>8.139359000000001</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="7" t="n">
         <v>0.2144921595974862</v>
       </c>
     </row>
@@ -3475,13 +4056,13 @@
           <t>HPF</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>7.893821003975312</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>7.948546</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="7" t="n">
         <v>0.05472499602468872</v>
       </c>
     </row>
@@ -3491,13 +4072,13 @@
           <t>Isocortex</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>7.887883541151983</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>8.007250000000001</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="7" t="n">
         <v>0.1193664588480177</v>
       </c>
     </row>
@@ -3507,13 +4088,13 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>7.621401727281114</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>7.8678527</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="7" t="n">
         <v>0.2464509727188862</v>
       </c>
     </row>
@@ -3523,13 +4104,13 @@
           <t>P</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>7.540377059235904</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>7.9330397</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="7" t="n">
         <v>0.3926626407640965</v>
       </c>
     </row>
@@ -3539,13 +4120,13 @@
           <t>PAL</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>7.368485617585351</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>7.7508726</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="7" t="n">
         <v>0.3823869824146495</v>
       </c>
     </row>
@@ -3554,7 +4135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3566,7 +4147,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -3576,29 +4157,29 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>En yuksek 10 hucre tipi</t>
+          <t>En yüksek 10 hücre tipi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sira</t>
+          <t>Sıra</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sinif</t>
+          <t>Sınıf</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3621,10 +4202,10 @@
           <t>OPC-Oligo</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="4" t="n">
         <v>371211</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>7.765019914220215</v>
       </c>
     </row>
@@ -3634,7 +4215,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>OPC (oncul)</t>
+          <t>OPC (öncül)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3642,10 +4223,10 @@
           <t>OPC-Oligo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="4" t="n">
         <v>106459</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>6.764457360101072</v>
       </c>
     </row>
@@ -3663,10 +4244,10 @@
           <t>Medial habenula</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="4" t="n">
         <v>4662</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>6.757697807872158</v>
       </c>
     </row>
@@ -3684,10 +4265,10 @@
           <t>Medulla GABA</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="4" t="n">
         <v>716</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>6.679214888268157</v>
       </c>
     </row>
@@ -3705,10 +4286,10 @@
           <t>Medulla</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="4" t="n">
         <v>1725</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>6.041827412289855</v>
       </c>
     </row>
@@ -3726,10 +4307,10 @@
           <t>Medulla GABA</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="4" t="n">
         <v>623</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>5.679213168218299</v>
       </c>
     </row>
@@ -3747,10 +4328,10 @@
           <t>Medulla GABA</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="4" t="n">
         <v>1271</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>5.667426185680566</v>
       </c>
     </row>
@@ -3768,10 +4349,10 @@
           <t>Medulla GABA</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="4" t="n">
         <v>875</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>5.661107027771428</v>
       </c>
     </row>
@@ -3789,10 +4370,10 @@
           <t>Medulla GABA</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="4" t="n">
         <v>2312</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>5.643603335640138</v>
       </c>
     </row>
@@ -3810,10 +4391,10 @@
           <t>Hipotalamus</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="4" t="n">
         <v>3793</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>5.596371214025836</v>
       </c>
     </row>
@@ -3821,14 +4402,14 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Glia tipleri karsilastirmasi</t>
+          <t>Glia tipleri karşılaştırması</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Hucre tipi</t>
+          <t>Hücre tipi</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3838,7 +4419,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ifade eden oran</t>
+          <t>İfade eden oran</t>
         </is>
       </c>
     </row>
@@ -3848,10 +4429,10 @@
           <t>Olgun oligodendrosit</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>7.765019914220215</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="6" t="n">
         <v>0.9250264674268812</v>
       </c>
     </row>
@@ -3861,10 +4442,10 @@
           <t>OPC</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>6.764457360101072</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="6" t="n">
         <v>0.850797020449187</v>
       </c>
     </row>
@@ -3874,10 +4455,10 @@
           <t>Astrosit (telensefalik)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>3.772723433937706</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="6" t="n">
         <v>0.5096496806481047</v>
       </c>
     </row>
@@ -3887,10 +4468,10 @@
           <t>Mikroglia</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>3.879017706744648</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="6" t="n">
         <v>0.4917272191673212</v>
       </c>
     </row>
@@ -3900,10 +4481,10 @@
           <t>Endotel</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="5" t="n">
         <v>3.790201947700223</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="6" t="n">
         <v>0.4937763763099246</v>
       </c>
     </row>
@@ -3913,10 +4494,10 @@
           <t>Perisit</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>2.85009551456625</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="6" t="n">
         <v>0.3519205869659041</v>
       </c>
     </row>
@@ -3924,14 +4505,14 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>En dusuk hucreler</t>
+          <t>En düşük hücreler</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3941,7 +4522,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ifade eden oran</t>
+          <t>İfade eden oran</t>
         </is>
       </c>
     </row>
@@ -3951,10 +4532,10 @@
           <t>OB Trdn Gaba</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="5" t="n">
         <v>0.656512470708872</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="6" t="n">
         <v>0.09451627284886301</v>
       </c>
     </row>
@@ -3964,10 +4545,10 @@
           <t>OB-out Frmd7 Gaba</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>0.7941136664323259</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="6" t="n">
         <v>0.1127901883486639</v>
       </c>
     </row>
@@ -3977,10 +4558,10 @@
           <t>OB-STR-CTX Inh IMN</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="5" t="n">
         <v>1.203411173657884</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="6" t="n">
         <v>0.1743668066692121</v>
       </c>
     </row>
@@ -3990,10 +4571,10 @@
           <t>OB-in Frmd7 Gaba</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>1.267535100730406</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="6" t="n">
         <v>0.1935426169394508</v>
       </c>
     </row>
@@ -4003,10 +4584,10 @@
           <t>Sncg Gaba (korteks)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>1.978274600239391</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="6" t="n">
         <v>0.3862894450489662</v>
       </c>
     </row>
@@ -4016,10 +4597,10 @@
           <t>Vip Gaba (korteks)</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>2.217751568167665</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="6" t="n">
         <v>0.3680239520958083</v>
       </c>
     </row>
@@ -4027,34 +4608,34 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Tam siralama, 265 alt sinif</t>
+          <t>Tam sıralama, 265 alt sınıf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Sira</t>
+          <t>Sıra</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sinif</t>
+          <t>Sınıf</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Notrotransmitter</t>
+          <t>Nörotransmitter</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4064,12 +4645,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ifade eden oran</t>
+          <t>İfade eden oran</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Parca sayisi</t>
+          <t>Parça sayısı</t>
         </is>
       </c>
     </row>
@@ -4088,13 +4669,13 @@
         </is>
       </c>
       <c r="D34" s="3" t="n"/>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="4" t="n">
         <v>371211</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="5" t="n">
         <v>7.765019914220215</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="9" t="n">
         <v>0.9250264674268812</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -4116,13 +4697,13 @@
         </is>
       </c>
       <c r="D35" s="3" t="n"/>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="4" t="n">
         <v>106459</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>6.764457360101072</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="9" t="n">
         <v>0.850797020449187</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -4148,13 +4729,13 @@
           <t>Chol</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="4" t="n">
         <v>4662</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="5" t="n">
         <v>6.757697807872158</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="9" t="n">
         <v>0.9163449163449164</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -4180,13 +4761,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="4" t="n">
         <v>716</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="5" t="n">
         <v>6.679214888268157</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="9" t="n">
         <v>0.939944134078212</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -4212,13 +4793,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="4" t="n">
         <v>1725</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="5" t="n">
         <v>6.041827412289855</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="9" t="n">
         <v>0.8782608695652174</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -4244,13 +4825,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="4" t="n">
         <v>623</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>5.679213168218299</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="9" t="n">
         <v>0.8747993579454254</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -4276,13 +4857,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="4" t="n">
         <v>1271</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="5" t="n">
         <v>5.667426185680566</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="9" t="n">
         <v>0.909520062942565</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -4308,13 +4889,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="4" t="n">
         <v>875</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="5" t="n">
         <v>5.661107027771428</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="9" t="n">
         <v>0.8822857142857143</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -4340,13 +4921,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E42" s="4" t="n">
         <v>2312</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="5" t="n">
         <v>5.643603335640138</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="9" t="n">
         <v>0.8680795847750865</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4372,13 +4953,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E43" s="4" t="n">
         <v>3793</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="5" t="n">
         <v>5.596371214025836</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="9" t="n">
         <v>0.8589506986554178</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4404,13 +4985,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="4" t="n">
         <v>1286</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>5.579057558709176</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G44" s="9" t="n">
         <v>0.8755832037325039</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4436,13 +5017,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="4" t="n">
         <v>536</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="5" t="n">
         <v>5.512645689365672</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>0.875</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4468,13 +5049,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="4" t="n">
         <v>607</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="5" t="n">
         <v>5.408853546952224</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="9" t="n">
         <v>0.8336079077429983</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4500,13 +5081,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="4" t="n">
         <v>2193</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="5" t="n">
         <v>5.408051833971728</v>
       </c>
-      <c r="G47" s="8" t="n">
+      <c r="G47" s="9" t="n">
         <v>0.8549931600547196</v>
       </c>
       <c r="H47" s="3" t="n">
@@ -4532,13 +5113,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="E48" s="4" t="n">
         <v>592</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="5" t="n">
         <v>5.404148</v>
       </c>
-      <c r="G48" s="8" t="n">
+      <c r="G48" s="9" t="n">
         <v>0.7753378378378378</v>
       </c>
       <c r="H48" s="3" t="n">
@@ -4564,13 +5145,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" s="4" t="n">
         <v>5855</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="5" t="n">
         <v>5.40128637233134</v>
       </c>
-      <c r="G49" s="8" t="n">
+      <c r="G49" s="9" t="n">
         <v>0.8695132365499573</v>
       </c>
       <c r="H49" s="3" t="n">
@@ -4596,13 +5177,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="4" t="n">
         <v>1289</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="5" t="n">
         <v>5.394826210628393</v>
       </c>
-      <c r="G50" s="8" t="n">
+      <c r="G50" s="9" t="n">
         <v>0.8502715283165244</v>
       </c>
       <c r="H50" s="3" t="n">
@@ -4628,13 +5209,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n">
+      <c r="E51" s="4" t="n">
         <v>1659</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="5" t="n">
         <v>5.373385795177819</v>
       </c>
-      <c r="G51" s="8" t="n">
+      <c r="G51" s="9" t="n">
         <v>0.8625678119349005</v>
       </c>
       <c r="H51" s="3" t="n">
@@ -4656,13 +5237,13 @@
         </is>
       </c>
       <c r="D52" s="3" t="n"/>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="4" t="n">
         <v>824</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="5" t="n">
         <v>5.370262845388349</v>
       </c>
-      <c r="G52" s="8" t="n">
+      <c r="G52" s="9" t="n">
         <v>0.7354368932038835</v>
       </c>
       <c r="H52" s="3" t="n">
@@ -4688,13 +5269,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E53" s="4" t="n">
         <v>1418</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="5" t="n">
         <v>5.342422598166432</v>
       </c>
-      <c r="G53" s="8" t="n">
+      <c r="G53" s="9" t="n">
         <v>0.892101551480959</v>
       </c>
       <c r="H53" s="3" t="n">
@@ -4720,13 +5301,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n">
+      <c r="E54" s="4" t="n">
         <v>1973</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="5" t="n">
         <v>5.336755669488089</v>
       </c>
-      <c r="G54" s="8" t="n">
+      <c r="G54" s="9" t="n">
         <v>0.8550430816016219</v>
       </c>
       <c r="H54" s="3" t="n">
@@ -4752,13 +5333,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n">
+      <c r="E55" s="4" t="n">
         <v>4509</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="5" t="n">
         <v>5.313934810955866</v>
       </c>
-      <c r="G55" s="8" t="n">
+      <c r="G55" s="9" t="n">
         <v>0.8272344200487914</v>
       </c>
       <c r="H55" s="3" t="n">
@@ -4784,13 +5365,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E56" s="4" t="n">
         <v>2145</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="5" t="n">
         <v>5.287605897249417</v>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="G56" s="9" t="n">
         <v>0.8391608391608392</v>
       </c>
       <c r="H56" s="3" t="n">
@@ -4816,13 +5397,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" s="4" t="n">
         <v>2746</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="5" t="n">
         <v>5.267151498324837</v>
       </c>
-      <c r="G57" s="8" t="n">
+      <c r="G57" s="9" t="n">
         <v>0.8415877640203933</v>
       </c>
       <c r="H57" s="3" t="n">
@@ -4848,13 +5429,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n">
+      <c r="E58" s="4" t="n">
         <v>1666</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="5" t="n">
         <v>5.25058140942377</v>
       </c>
-      <c r="G58" s="8" t="n">
+      <c r="G58" s="9" t="n">
         <v>0.8331332533013205</v>
       </c>
       <c r="H58" s="3" t="n">
@@ -4880,13 +5461,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E59" s="4" t="n">
         <v>133778</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="5" t="n">
         <v>5.213353685630671</v>
       </c>
-      <c r="G59" s="8" t="n">
+      <c r="G59" s="9" t="n">
         <v>0.6654532135328679</v>
       </c>
       <c r="H59" s="3" t="n">
@@ -4912,13 +5493,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E60" s="4" t="n">
         <v>3564</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="5" t="n">
         <v>5.182288065207632</v>
       </c>
-      <c r="G60" s="8" t="n">
+      <c r="G60" s="9" t="n">
         <v>0.8372615039281706</v>
       </c>
       <c r="H60" s="3" t="n">
@@ -4944,13 +5525,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E61" s="4" t="n">
         <v>5226</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="5" t="n">
         <v>5.178536690298508</v>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="G61" s="9" t="n">
         <v>0.8067355530042097</v>
       </c>
       <c r="H61" s="3" t="n">
@@ -4976,13 +5557,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n">
+      <c r="E62" s="4" t="n">
         <v>1882</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="5" t="n">
         <v>5.171220831827843</v>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="G62" s="9" t="n">
         <v>0.842720510095643</v>
       </c>
       <c r="H62" s="3" t="n">
@@ -5008,13 +5589,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="4" t="n">
         <v>3087</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="5" t="n">
         <v>5.133808227858762</v>
       </c>
-      <c r="G63" s="8" t="n">
+      <c r="G63" s="9" t="n">
         <v>0.7952704891480402</v>
       </c>
       <c r="H63" s="3" t="n">
@@ -5040,13 +5621,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" s="4" t="n">
         <v>2099</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="5" t="n">
         <v>5.101512344830871</v>
       </c>
-      <c r="G64" s="8" t="n">
+      <c r="G64" s="9" t="n">
         <v>0.7965697951405432</v>
       </c>
       <c r="H64" s="3" t="n">
@@ -5072,13 +5653,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="4" t="n">
         <v>3425</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="5" t="n">
         <v>5.058398011737226</v>
       </c>
-      <c r="G65" s="8" t="n">
+      <c r="G65" s="9" t="n">
         <v>0.877956204379562</v>
       </c>
       <c r="H65" s="3" t="n">
@@ -5104,13 +5685,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="4" t="n">
         <v>768</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="5" t="n">
         <v>5.055110953125</v>
       </c>
-      <c r="G66" s="8" t="n">
+      <c r="G66" s="9" t="n">
         <v>0.7942708333333334</v>
       </c>
       <c r="H66" s="3" t="n">
@@ -5132,13 +5713,13 @@
         </is>
       </c>
       <c r="D67" s="3" t="n"/>
-      <c r="E67" s="7" t="n">
+      <c r="E67" s="4" t="n">
         <v>1004</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="F67" s="5" t="n">
         <v>5.04447215816733</v>
       </c>
-      <c r="G67" s="8" t="n">
+      <c r="G67" s="9" t="n">
         <v>0.6852589641434262</v>
       </c>
       <c r="H67" s="3" t="n">
@@ -5164,13 +5745,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="4" t="n">
         <v>1702</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="5" t="n">
         <v>5.033577967097532</v>
       </c>
-      <c r="G68" s="8" t="n">
+      <c r="G68" s="9" t="n">
         <v>0.8225616921269095</v>
       </c>
       <c r="H68" s="3" t="n">
@@ -5196,13 +5777,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="5" t="n">
         <v>5.032489972500001</v>
       </c>
-      <c r="G69" s="8" t="n">
+      <c r="G69" s="9" t="n">
         <v>0.83375</v>
       </c>
       <c r="H69" s="3" t="n">
@@ -5228,13 +5809,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E70" s="7" t="n">
+      <c r="E70" s="4" t="n">
         <v>1951</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="5" t="n">
         <v>5.030775459764223</v>
       </c>
-      <c r="G70" s="8" t="n">
+      <c r="G70" s="9" t="n">
         <v>0.8124038954382368</v>
       </c>
       <c r="H70" s="3" t="n">
@@ -5260,13 +5841,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="4" t="n">
         <v>542</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="5" t="n">
         <v>5.030028789852399</v>
       </c>
-      <c r="G71" s="8" t="n">
+      <c r="G71" s="9" t="n">
         <v>0.8413284132841329</v>
       </c>
       <c r="H71" s="3" t="n">
@@ -5292,13 +5873,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E72" s="4" t="n">
         <v>1275</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="5" t="n">
         <v>5.025811823372549</v>
       </c>
-      <c r="G72" s="8" t="n">
+      <c r="G72" s="9" t="n">
         <v>0.807843137254902</v>
       </c>
       <c r="H72" s="3" t="n">
@@ -5324,13 +5905,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n">
+      <c r="E73" s="4" t="n">
         <v>1943</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="5" t="n">
         <v>5.018579577354607</v>
       </c>
-      <c r="G73" s="8" t="n">
+      <c r="G73" s="9" t="n">
         <v>0.8069994853319609</v>
       </c>
       <c r="H73" s="3" t="n">
@@ -5356,13 +5937,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n">
+      <c r="E74" s="4" t="n">
         <v>2216</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="5" t="n">
         <v>5.002568691832131</v>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G74" s="9" t="n">
         <v>0.7788808664259927</v>
       </c>
       <c r="H74" s="3" t="n">
@@ -5388,13 +5969,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E75" s="4" t="n">
         <v>1129</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="5" t="n">
         <v>4.984948</v>
       </c>
-      <c r="G75" s="8" t="n">
+      <c r="G75" s="9" t="n">
         <v>0.7803365810451727</v>
       </c>
       <c r="H75" s="3" t="n">
@@ -5420,13 +6001,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n">
+      <c r="E76" s="4" t="n">
         <v>1191</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="5" t="n">
         <v>4.980223737699412</v>
       </c>
-      <c r="G76" s="8" t="n">
+      <c r="G76" s="9" t="n">
         <v>0.7959697732997482</v>
       </c>
       <c r="H76" s="3" t="n">
@@ -5452,13 +6033,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E77" s="7" t="n">
+      <c r="E77" s="4" t="n">
         <v>4055</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="5" t="n">
         <v>4.939940250406905</v>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="9" t="n">
         <v>0.7718865598027127</v>
       </c>
       <c r="H77" s="3" t="n">
@@ -5484,13 +6065,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E78" s="7" t="n">
+      <c r="E78" s="4" t="n">
         <v>2942</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="5" t="n">
         <v>4.932734414072059</v>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="9" t="n">
         <v>0.8076138681169273</v>
       </c>
       <c r="H78" s="3" t="n">
@@ -5516,13 +6097,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E79" s="7" t="n">
+      <c r="E79" s="4" t="n">
         <v>1426</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="5" t="n">
         <v>4.909536312272089</v>
       </c>
-      <c r="G79" s="8" t="n">
+      <c r="G79" s="9" t="n">
         <v>0.7468443197755961</v>
       </c>
       <c r="H79" s="3" t="n">
@@ -5548,13 +6129,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E80" s="7" t="n">
+      <c r="E80" s="4" t="n">
         <v>910</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="5" t="n">
         <v>4.908212078351649</v>
       </c>
-      <c r="G80" s="8" t="n">
+      <c r="G80" s="9" t="n">
         <v>0.7725274725274726</v>
       </c>
       <c r="H80" s="3" t="n">
@@ -5580,13 +6161,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E81" s="7" t="n">
+      <c r="E81" s="4" t="n">
         <v>3497</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="5" t="n">
         <v>4.887739479525307</v>
       </c>
-      <c r="G81" s="8" t="n">
+      <c r="G81" s="9" t="n">
         <v>0.7806691449814126</v>
       </c>
       <c r="H81" s="3" t="n">
@@ -5612,13 +6193,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E82" s="7" t="n">
+      <c r="E82" s="4" t="n">
         <v>2703</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="5" t="n">
         <v>4.886765109285979</v>
       </c>
-      <c r="G82" s="8" t="n">
+      <c r="G82" s="9" t="n">
         <v>0.8261191268960414</v>
       </c>
       <c r="H82" s="3" t="n">
@@ -5644,13 +6225,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E83" s="7" t="n">
+      <c r="E83" s="4" t="n">
         <v>1296</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="5" t="n">
         <v>4.877574352006173</v>
       </c>
-      <c r="G83" s="8" t="n">
+      <c r="G83" s="9" t="n">
         <v>0.7716049382716049</v>
       </c>
       <c r="H83" s="3" t="n">
@@ -5676,13 +6257,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E84" s="7" t="n">
+      <c r="E84" s="4" t="n">
         <v>1107</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="5" t="n">
         <v>4.860091536133695</v>
       </c>
-      <c r="G84" s="8" t="n">
+      <c r="G84" s="9" t="n">
         <v>0.7985546522131888</v>
       </c>
       <c r="H84" s="3" t="n">
@@ -5708,13 +6289,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E85" s="7" t="n">
+      <c r="E85" s="4" t="n">
         <v>951</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="5" t="n">
         <v>4.857361367402733</v>
       </c>
-      <c r="G85" s="8" t="n">
+      <c r="G85" s="9" t="n">
         <v>0.7875920084121977</v>
       </c>
       <c r="H85" s="3" t="n">
@@ -5740,13 +6321,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E86" s="7" t="n">
+      <c r="E86" s="4" t="n">
         <v>2165</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="5" t="n">
         <v>4.830168341154734</v>
       </c>
-      <c r="G86" s="8" t="n">
+      <c r="G86" s="9" t="n">
         <v>0.7325635103926097</v>
       </c>
       <c r="H86" s="3" t="n">
@@ -5772,13 +6353,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E87" s="7" t="n">
+      <c r="E87" s="4" t="n">
         <v>1105</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="5" t="n">
         <v>4.828784452579186</v>
       </c>
-      <c r="G87" s="8" t="n">
+      <c r="G87" s="9" t="n">
         <v>0.7873303167420814</v>
       </c>
       <c r="H87" s="3" t="n">
@@ -5804,13 +6385,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E88" s="7" t="n">
+      <c r="E88" s="4" t="n">
         <v>1413</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="5" t="n">
         <v>4.819603924769994</v>
       </c>
-      <c r="G88" s="8" t="n">
+      <c r="G88" s="9" t="n">
         <v>0.7876857749469215</v>
       </c>
       <c r="H88" s="3" t="n">
@@ -5836,13 +6417,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E89" s="7" t="n">
+      <c r="E89" s="4" t="n">
         <v>1754</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="5" t="n">
         <v>4.817880724515394</v>
       </c>
-      <c r="G89" s="8" t="n">
+      <c r="G89" s="9" t="n">
         <v>0.7611174458380844</v>
       </c>
       <c r="H89" s="3" t="n">
@@ -5868,13 +6449,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E90" s="7" t="n">
+      <c r="E90" s="4" t="n">
         <v>518</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="5" t="n">
         <v>4.817842577606178</v>
       </c>
-      <c r="G90" s="8" t="n">
+      <c r="G90" s="9" t="n">
         <v>0.7953667953667953</v>
       </c>
       <c r="H90" s="3" t="n">
@@ -5900,13 +6481,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E91" s="7" t="n">
+      <c r="E91" s="4" t="n">
         <v>3519</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="5" t="n">
         <v>4.81205645069622</v>
       </c>
-      <c r="G91" s="8" t="n">
+      <c r="G91" s="9" t="n">
         <v>0.7868712702472294</v>
       </c>
       <c r="H91" s="3" t="n">
@@ -5932,13 +6513,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E92" s="7" t="n">
+      <c r="E92" s="4" t="n">
         <v>561</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="F92" s="5" t="n">
         <v>4.809231432085562</v>
       </c>
-      <c r="G92" s="8" t="n">
+      <c r="G92" s="9" t="n">
         <v>0.7932263814616756</v>
       </c>
       <c r="H92" s="3" t="n">
@@ -5964,13 +6545,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n">
+      <c r="E93" s="4" t="n">
         <v>2308</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="5" t="n">
         <v>4.80508876347487</v>
       </c>
-      <c r="G93" s="8" t="n">
+      <c r="G93" s="9" t="n">
         <v>0.7790294627383015</v>
       </c>
       <c r="H93" s="3" t="n">
@@ -5996,13 +6577,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E94" s="7" t="n">
+      <c r="E94" s="4" t="n">
         <v>2950</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="5" t="n">
         <v>4.80229300759322</v>
       </c>
-      <c r="G94" s="8" t="n">
+      <c r="G94" s="9" t="n">
         <v>0.763728813559322</v>
       </c>
       <c r="H94" s="3" t="n">
@@ -6028,13 +6609,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E95" s="7" t="n">
+      <c r="E95" s="4" t="n">
         <v>1905</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="5" t="n">
         <v>4.800138625301837</v>
       </c>
-      <c r="G95" s="8" t="n">
+      <c r="G95" s="9" t="n">
         <v>0.7627296587926509</v>
       </c>
       <c r="H95" s="3" t="n">
@@ -6060,13 +6641,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n">
+      <c r="E96" s="4" t="n">
         <v>1749</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="5" t="n">
         <v>4.797431749056605</v>
       </c>
-      <c r="G96" s="8" t="n">
+      <c r="G96" s="9" t="n">
         <v>0.7712978845054317</v>
       </c>
       <c r="H96" s="3" t="n">
@@ -6092,13 +6673,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n">
+      <c r="E97" s="4" t="n">
         <v>2915</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="5" t="n">
         <v>4.794875217941681</v>
       </c>
-      <c r="G97" s="8" t="n">
+      <c r="G97" s="9" t="n">
         <v>0.7656946826758148</v>
       </c>
       <c r="H97" s="3" t="n">
@@ -6124,13 +6705,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E98" s="7" t="n">
+      <c r="E98" s="4" t="n">
         <v>1522</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="5" t="n">
         <v>4.794762600788436</v>
       </c>
-      <c r="G98" s="8" t="n">
+      <c r="G98" s="9" t="n">
         <v>0.7647831800262812</v>
       </c>
       <c r="H98" s="3" t="n">
@@ -6156,13 +6737,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n">
+      <c r="E99" s="4" t="n">
         <v>1122</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="5" t="n">
         <v>4.783795751336898</v>
       </c>
-      <c r="G99" s="8" t="n">
+      <c r="G99" s="9" t="n">
         <v>0.785204991087344</v>
       </c>
       <c r="H99" s="3" t="n">
@@ -6188,13 +6769,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n">
+      <c r="E100" s="4" t="n">
         <v>960</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="5" t="n">
         <v>4.7721925</v>
       </c>
-      <c r="G100" s="8" t="n">
+      <c r="G100" s="9" t="n">
         <v>0.7354166666666667</v>
       </c>
       <c r="H100" s="3" t="n">
@@ -6220,13 +6801,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E101" s="7" t="n">
+      <c r="E101" s="4" t="n">
         <v>1349</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="5" t="n">
         <v>4.771060882876204</v>
       </c>
-      <c r="G101" s="8" t="n">
+      <c r="G101" s="9" t="n">
         <v>0.7242401779095626</v>
       </c>
       <c r="H101" s="3" t="n">
@@ -6252,13 +6833,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n">
+      <c r="E102" s="4" t="n">
         <v>6570</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="5" t="n">
         <v>4.769509298493151</v>
       </c>
-      <c r="G102" s="8" t="n">
+      <c r="G102" s="9" t="n">
         <v>0.776103500761035</v>
       </c>
       <c r="H102" s="3" t="n">
@@ -6284,13 +6865,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n">
+      <c r="E103" s="4" t="n">
         <v>3251</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="5" t="n">
         <v>4.768354658997231</v>
       </c>
-      <c r="G103" s="8" t="n">
+      <c r="G103" s="9" t="n">
         <v>0.8046754844663181</v>
       </c>
       <c r="H103" s="3" t="n">
@@ -6316,13 +6897,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E104" s="7" t="n">
+      <c r="E104" s="4" t="n">
         <v>1091</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="5" t="n">
         <v>4.766043290284143</v>
       </c>
-      <c r="G104" s="8" t="n">
+      <c r="G104" s="9" t="n">
         <v>0.7598533455545371</v>
       </c>
       <c r="H104" s="3" t="n">
@@ -6348,13 +6929,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n">
+      <c r="E105" s="4" t="n">
         <v>778</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="5" t="n">
         <v>4.765489179691516</v>
       </c>
-      <c r="G105" s="8" t="n">
+      <c r="G105" s="9" t="n">
         <v>0.7827763496143959</v>
       </c>
       <c r="H105" s="3" t="n">
@@ -6380,13 +6961,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E106" s="7" t="n">
+      <c r="E106" s="4" t="n">
         <v>2455</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="5" t="n">
         <v>4.761133768839104</v>
       </c>
-      <c r="G106" s="8" t="n">
+      <c r="G106" s="9" t="n">
         <v>0.7963340122199593</v>
       </c>
       <c r="H106" s="3" t="n">
@@ -6412,13 +6993,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E107" s="7" t="n">
+      <c r="E107" s="4" t="n">
         <v>3889</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="5" t="n">
         <v>4.756499442041656</v>
       </c>
-      <c r="G107" s="8" t="n">
+      <c r="G107" s="9" t="n">
         <v>0.8079197737207509</v>
       </c>
       <c r="H107" s="3" t="n">
@@ -6444,13 +7025,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E108" s="7" t="n">
+      <c r="E108" s="4" t="n">
         <v>883</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="5" t="n">
         <v>4.753203264665912</v>
       </c>
-      <c r="G108" s="8" t="n">
+      <c r="G108" s="9" t="n">
         <v>0.782559456398641</v>
       </c>
       <c r="H108" s="3" t="n">
@@ -6476,13 +7057,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E109" s="7" t="n">
+      <c r="E109" s="4" t="n">
         <v>3641</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="5" t="n">
         <v>4.751001994507004</v>
       </c>
-      <c r="G109" s="8" t="n">
+      <c r="G109" s="9" t="n">
         <v>0.784674539961549</v>
       </c>
       <c r="H109" s="3" t="n">
@@ -6508,13 +7089,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E110" s="7" t="n">
+      <c r="E110" s="4" t="n">
         <v>3090</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="F110" s="5" t="n">
         <v>4.745617904207119</v>
       </c>
-      <c r="G110" s="8" t="n">
+      <c r="G110" s="9" t="n">
         <v>0.7644012944983819</v>
       </c>
       <c r="H110" s="3" t="n">
@@ -6540,13 +7121,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E111" s="7" t="n">
+      <c r="E111" s="4" t="n">
         <v>1973</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="5" t="n">
         <v>4.740257059706031</v>
       </c>
-      <c r="G111" s="8" t="n">
+      <c r="G111" s="9" t="n">
         <v>0.7729346173340091</v>
       </c>
       <c r="H111" s="3" t="n">
@@ -6572,13 +7153,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E112" s="7" t="n">
+      <c r="E112" s="4" t="n">
         <v>3333</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="5" t="n">
         <v>4.734984609510951</v>
       </c>
-      <c r="G112" s="8" t="n">
+      <c r="G112" s="9" t="n">
         <v>0.7755775577557755</v>
       </c>
       <c r="H112" s="3" t="n">
@@ -6604,13 +7185,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E113" s="7" t="n">
+      <c r="E113" s="4" t="n">
         <v>1912</v>
       </c>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="5" t="n">
         <v>4.726149527458159</v>
       </c>
-      <c r="G113" s="8" t="n">
+      <c r="G113" s="9" t="n">
         <v>0.7698744769874477</v>
       </c>
       <c r="H113" s="3" t="n">
@@ -6636,13 +7217,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E114" s="7" t="n">
+      <c r="E114" s="4" t="n">
         <v>1599</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="5" t="n">
         <v>4.718408177923702</v>
       </c>
-      <c r="G114" s="8" t="n">
+      <c r="G114" s="9" t="n">
         <v>0.7879924953095685</v>
       </c>
       <c r="H114" s="3" t="n">
@@ -6668,13 +7249,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E115" s="7" t="n">
+      <c r="E115" s="4" t="n">
         <v>3440</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="5" t="n">
         <v>4.698692105523255</v>
       </c>
-      <c r="G115" s="8" t="n">
+      <c r="G115" s="9" t="n">
         <v>0.7709302325581395</v>
       </c>
       <c r="H115" s="3" t="n">
@@ -6700,13 +7281,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E116" s="7" t="n">
+      <c r="E116" s="4" t="n">
         <v>3511</v>
       </c>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="5" t="n">
         <v>4.688263650156651</v>
       </c>
-      <c r="G116" s="8" t="n">
+      <c r="G116" s="9" t="n">
         <v>0.779549985759043</v>
       </c>
       <c r="H116" s="3" t="n">
@@ -6732,13 +7313,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n">
+      <c r="E117" s="4" t="n">
         <v>3086</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="5" t="n">
         <v>4.670260961179521</v>
       </c>
-      <c r="G117" s="8" t="n">
+      <c r="G117" s="9" t="n">
         <v>0.7508101101749838</v>
       </c>
       <c r="H117" s="3" t="n">
@@ -6764,13 +7345,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E118" s="7" t="n">
+      <c r="E118" s="4" t="n">
         <v>1287</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="5" t="n">
         <v>4.669597322921523</v>
       </c>
-      <c r="G118" s="8" t="n">
+      <c r="G118" s="9" t="n">
         <v>0.7668997668997669</v>
       </c>
       <c r="H118" s="3" t="n">
@@ -6796,13 +7377,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E119" s="7" t="n">
+      <c r="E119" s="4" t="n">
         <v>3943</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="5" t="n">
         <v>4.658206196931271</v>
       </c>
-      <c r="G119" s="8" t="n">
+      <c r="G119" s="9" t="n">
         <v>0.7722546284554908</v>
       </c>
       <c r="H119" s="3" t="n">
@@ -6828,13 +7409,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E120" s="7" t="n">
+      <c r="E120" s="4" t="n">
         <v>2972</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="5" t="n">
         <v>4.64271063923284</v>
       </c>
-      <c r="G120" s="8" t="n">
+      <c r="G120" s="9" t="n">
         <v>0.753028263795424</v>
       </c>
       <c r="H120" s="3" t="n">
@@ -6860,13 +7441,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E121" s="7" t="n">
+      <c r="E121" s="4" t="n">
         <v>986</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="5" t="n">
         <v>4.640082831237322</v>
       </c>
-      <c r="G121" s="8" t="n">
+      <c r="G121" s="9" t="n">
         <v>0.781947261663286</v>
       </c>
       <c r="H121" s="3" t="n">
@@ -6892,13 +7473,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E122" s="7" t="n">
+      <c r="E122" s="4" t="n">
         <v>3632</v>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="5" t="n">
         <v>4.639798919383259</v>
       </c>
-      <c r="G122" s="8" t="n">
+      <c r="G122" s="9" t="n">
         <v>0.7670704845814978</v>
       </c>
       <c r="H122" s="3" t="n">
@@ -6924,13 +7505,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n">
+      <c r="E123" s="4" t="n">
         <v>753</v>
       </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="5" t="n">
         <v>4.628655934926959</v>
       </c>
-      <c r="G123" s="8" t="n">
+      <c r="G123" s="9" t="n">
         <v>0.8406374501992032</v>
       </c>
       <c r="H123" s="3" t="n">
@@ -6956,13 +7537,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E124" s="7" t="n">
+      <c r="E124" s="4" t="n">
         <v>513</v>
       </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="5" t="n">
         <v>4.618056229434698</v>
       </c>
-      <c r="G124" s="8" t="n">
+      <c r="G124" s="9" t="n">
         <v>0.7524366471734892</v>
       </c>
       <c r="H124" s="3" t="n">
@@ -6988,13 +7569,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E125" s="7" t="n">
+      <c r="E125" s="4" t="n">
         <v>3419</v>
       </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="5" t="n">
         <v>4.607646419830361</v>
       </c>
-      <c r="G125" s="8" t="n">
+      <c r="G125" s="9" t="n">
         <v>0.7554840596665692</v>
       </c>
       <c r="H125" s="3" t="n">
@@ -7020,13 +7601,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n">
+      <c r="E126" s="4" t="n">
         <v>1052</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="5" t="n">
         <v>4.587401291920152</v>
       </c>
-      <c r="G126" s="8" t="n">
+      <c r="G126" s="9" t="n">
         <v>0.7461977186311787</v>
       </c>
       <c r="H126" s="3" t="n">
@@ -7052,13 +7633,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E127" s="7" t="n">
+      <c r="E127" s="4" t="n">
         <v>1141</v>
       </c>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="5" t="n">
         <v>4.583016510078878</v>
       </c>
-      <c r="G127" s="8" t="n">
+      <c r="G127" s="9" t="n">
         <v>0.7414548641542507</v>
       </c>
       <c r="H127" s="3" t="n">
@@ -7084,13 +7665,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E128" s="7" t="n">
+      <c r="E128" s="4" t="n">
         <v>1464</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="5" t="n">
         <v>4.579507249385246</v>
       </c>
-      <c r="G128" s="8" t="n">
+      <c r="G128" s="9" t="n">
         <v>0.7752732240437158</v>
       </c>
       <c r="H128" s="3" t="n">
@@ -7116,13 +7697,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E129" s="7" t="n">
+      <c r="E129" s="4" t="n">
         <v>5234</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="F129" s="5" t="n">
         <v>4.578996540695452</v>
       </c>
-      <c r="G129" s="8" t="n">
+      <c r="G129" s="9" t="n">
         <v>0.8011081390905617</v>
       </c>
       <c r="H129" s="3" t="n">
@@ -7148,13 +7729,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E130" s="7" t="n">
+      <c r="E130" s="4" t="n">
         <v>3770</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="5" t="n">
         <v>4.578652188328912</v>
       </c>
-      <c r="G130" s="8" t="n">
+      <c r="G130" s="9" t="n">
         <v>0.7726790450928382</v>
       </c>
       <c r="H130" s="3" t="n">
@@ -7180,13 +7761,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E131" s="7" t="n">
+      <c r="E131" s="4" t="n">
         <v>6065</v>
       </c>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="5" t="n">
         <v>4.568469504369332</v>
       </c>
-      <c r="G131" s="8" t="n">
+      <c r="G131" s="9" t="n">
         <v>0.7873042044517725</v>
       </c>
       <c r="H131" s="3" t="n">
@@ -7212,13 +7793,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E132" s="7" t="n">
+      <c r="E132" s="4" t="n">
         <v>1560</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="5" t="n">
         <v>4.564542584615384</v>
       </c>
-      <c r="G132" s="8" t="n">
+      <c r="G132" s="9" t="n">
         <v>0.7352564102564103</v>
       </c>
       <c r="H132" s="3" t="n">
@@ -7244,13 +7825,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E133" s="7" t="n">
+      <c r="E133" s="4" t="n">
         <v>848</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="5" t="n">
         <v>4.558845718160377</v>
       </c>
-      <c r="G133" s="8" t="n">
+      <c r="G133" s="9" t="n">
         <v>0.8183962264150944</v>
       </c>
       <c r="H133" s="3" t="n">
@@ -7276,13 +7857,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E134" s="7" t="n">
+      <c r="E134" s="4" t="n">
         <v>2720</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="5" t="n">
         <v>4.547657265514705</v>
       </c>
-      <c r="G134" s="8" t="n">
+      <c r="G134" s="9" t="n">
         <v>0.7242647058823529</v>
       </c>
       <c r="H134" s="3" t="n">
@@ -7308,13 +7889,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E135" s="7" t="n">
+      <c r="E135" s="4" t="n">
         <v>2095</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="5" t="n">
         <v>4.546263511789976</v>
       </c>
-      <c r="G135" s="8" t="n">
+      <c r="G135" s="9" t="n">
         <v>0.7236276849642005</v>
       </c>
       <c r="H135" s="3" t="n">
@@ -7340,13 +7921,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E136" s="7" t="n">
+      <c r="E136" s="4" t="n">
         <v>6341</v>
       </c>
-      <c r="F136" s="4" t="n">
+      <c r="F136" s="5" t="n">
         <v>4.532238846175682</v>
       </c>
-      <c r="G136" s="8" t="n">
+      <c r="G136" s="9" t="n">
         <v>0.7211796246648794</v>
       </c>
       <c r="H136" s="3" t="n">
@@ -7372,13 +7953,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E137" s="7" t="n">
+      <c r="E137" s="4" t="n">
         <v>2337</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="5" t="n">
         <v>4.523936038254171</v>
       </c>
-      <c r="G137" s="8" t="n">
+      <c r="G137" s="9" t="n">
         <v>0.6863500213949508</v>
       </c>
       <c r="H137" s="3" t="n">
@@ -7404,13 +7985,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E138" s="7" t="n">
+      <c r="E138" s="4" t="n">
         <v>6280</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="5" t="n">
         <v>4.517861036464968</v>
       </c>
-      <c r="G138" s="8" t="n">
+      <c r="G138" s="9" t="n">
         <v>0.7378980891719745</v>
       </c>
       <c r="H138" s="3" t="n">
@@ -7436,13 +8017,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E139" s="7" t="n">
+      <c r="E139" s="4" t="n">
         <v>5207</v>
       </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="5" t="n">
         <v>4.514764042788554</v>
       </c>
-      <c r="G139" s="8" t="n">
+      <c r="G139" s="9" t="n">
         <v>0.7211446130209334</v>
       </c>
       <c r="H139" s="3" t="n">
@@ -7468,13 +8049,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E140" s="7" t="n">
+      <c r="E140" s="4" t="n">
         <v>4963</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="5" t="n">
         <v>4.512619528974411</v>
       </c>
-      <c r="G140" s="8" t="n">
+      <c r="G140" s="9" t="n">
         <v>0.7451138424340117</v>
       </c>
       <c r="H140" s="3" t="n">
@@ -7500,13 +8081,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E141" s="7" t="n">
+      <c r="E141" s="4" t="n">
         <v>2433</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="5" t="n">
         <v>4.511250296876284</v>
       </c>
-      <c r="G141" s="8" t="n">
+      <c r="G141" s="9" t="n">
         <v>0.7307850390464448</v>
       </c>
       <c r="H141" s="3" t="n">
@@ -7532,13 +8113,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E142" s="7" t="n">
+      <c r="E142" s="4" t="n">
         <v>4159</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="5" t="n">
         <v>4.510905590718922</v>
       </c>
-      <c r="G142" s="8" t="n">
+      <c r="G142" s="9" t="n">
         <v>0.740322192834816</v>
       </c>
       <c r="H142" s="3" t="n">
@@ -7564,13 +8145,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E143" s="7" t="n">
+      <c r="E143" s="4" t="n">
         <v>3131</v>
       </c>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="5" t="n">
         <v>4.504173956978601</v>
       </c>
-      <c r="G143" s="8" t="n">
+      <c r="G143" s="9" t="n">
         <v>0.7563078888534015</v>
       </c>
       <c r="H143" s="3" t="n">
@@ -7596,13 +8177,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E144" s="7" t="n">
+      <c r="E144" s="4" t="n">
         <v>8980</v>
       </c>
-      <c r="F144" s="4" t="n">
+      <c r="F144" s="5" t="n">
         <v>4.500414143997772</v>
       </c>
-      <c r="G144" s="8" t="n">
+      <c r="G144" s="9" t="n">
         <v>0.7079064587973274</v>
       </c>
       <c r="H144" s="3" t="n">
@@ -7628,13 +8209,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E145" s="7" t="n">
+      <c r="E145" s="4" t="n">
         <v>4667</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="5" t="n">
         <v>4.49806405228198</v>
       </c>
-      <c r="G145" s="8" t="n">
+      <c r="G145" s="9" t="n">
         <v>0.7171630597814442</v>
       </c>
       <c r="H145" s="3" t="n">
@@ -7660,13 +8241,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E146" s="7" t="n">
+      <c r="E146" s="4" t="n">
         <v>4186</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="5" t="n">
         <v>4.495154857142857</v>
       </c>
-      <c r="G146" s="8" t="n">
+      <c r="G146" s="9" t="n">
         <v>0.7663640707118968</v>
       </c>
       <c r="H146" s="3" t="n">
@@ -7692,13 +8273,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E147" s="7" t="n">
+      <c r="E147" s="4" t="n">
         <v>2906</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="5" t="n">
         <v>4.463920175017206</v>
       </c>
-      <c r="G147" s="8" t="n">
+      <c r="G147" s="9" t="n">
         <v>0.7219545767377838</v>
       </c>
       <c r="H147" s="3" t="n">
@@ -7724,13 +8305,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E148" s="7" t="n">
+      <c r="E148" s="4" t="n">
         <v>592</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="5" t="n">
         <v>4.461867672466216</v>
       </c>
-      <c r="G148" s="8" t="n">
+      <c r="G148" s="9" t="n">
         <v>0.7331081081081081</v>
       </c>
       <c r="H148" s="3" t="n">
@@ -7756,13 +8337,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E149" s="7" t="n">
+      <c r="E149" s="4" t="n">
         <v>11653</v>
       </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="5" t="n">
         <v>4.449599599304901</v>
       </c>
-      <c r="G149" s="8" t="n">
+      <c r="G149" s="9" t="n">
         <v>0.6757916416373466</v>
       </c>
       <c r="H149" s="3" t="n">
@@ -7788,13 +8369,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E150" s="7" t="n">
+      <c r="E150" s="4" t="n">
         <v>2008</v>
       </c>
-      <c r="F150" s="4" t="n">
+      <c r="F150" s="5" t="n">
         <v>4.438331809063746</v>
       </c>
-      <c r="G150" s="8" t="n">
+      <c r="G150" s="9" t="n">
         <v>0.7280876494023905</v>
       </c>
       <c r="H150" s="3" t="n">
@@ -7820,13 +8401,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E151" s="7" t="n">
+      <c r="E151" s="4" t="n">
         <v>1178</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="5" t="n">
         <v>4.435062354414262</v>
       </c>
-      <c r="G151" s="8" t="n">
+      <c r="G151" s="9" t="n">
         <v>0.7062818336162988</v>
       </c>
       <c r="H151" s="3" t="n">
@@ -7852,13 +8433,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E152" s="7" t="n">
+      <c r="E152" s="4" t="n">
         <v>2422</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="5" t="n">
         <v>4.4349319940545</v>
       </c>
-      <c r="G152" s="8" t="n">
+      <c r="G152" s="9" t="n">
         <v>0.763418662262593</v>
       </c>
       <c r="H152" s="3" t="n">
@@ -7884,13 +8465,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E153" s="7" t="n">
+      <c r="E153" s="4" t="n">
         <v>4424</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="5" t="n">
         <v>4.431648755221519</v>
       </c>
-      <c r="G153" s="8" t="n">
+      <c r="G153" s="9" t="n">
         <v>0.7081826401446655</v>
       </c>
       <c r="H153" s="3" t="n">
@@ -7912,13 +8493,13 @@
         </is>
       </c>
       <c r="D154" s="3" t="n"/>
-      <c r="E154" s="7" t="n">
+      <c r="E154" s="4" t="n">
         <v>13705</v>
       </c>
-      <c r="F154" s="4" t="n">
+      <c r="F154" s="5" t="n">
         <v>4.424467163531558</v>
       </c>
-      <c r="G154" s="8" t="n">
+      <c r="G154" s="9" t="n">
         <v>0.569500182415177</v>
       </c>
       <c r="H154" s="3" t="n">
@@ -7944,13 +8525,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E155" s="7" t="n">
+      <c r="E155" s="4" t="n">
         <v>1123</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="5" t="n">
         <v>4.418085083793411</v>
       </c>
-      <c r="G155" s="8" t="n">
+      <c r="G155" s="9" t="n">
         <v>0.7266251113089938</v>
       </c>
       <c r="H155" s="3" t="n">
@@ -7976,13 +8557,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E156" s="7" t="n">
+      <c r="E156" s="4" t="n">
         <v>3513</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="5" t="n">
         <v>4.4160871362653</v>
       </c>
-      <c r="G156" s="8" t="n">
+      <c r="G156" s="9" t="n">
         <v>0.7432393965271847</v>
       </c>
       <c r="H156" s="3" t="n">
@@ -8008,13 +8589,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E157" s="7" t="n">
+      <c r="E157" s="4" t="n">
         <v>1237</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="5" t="n">
         <v>4.412365601535974</v>
       </c>
-      <c r="G157" s="8" t="n">
+      <c r="G157" s="9" t="n">
         <v>0.7388843977364592</v>
       </c>
       <c r="H157" s="3" t="n">
@@ -8040,13 +8621,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E158" s="7" t="n">
+      <c r="E158" s="4" t="n">
         <v>1032</v>
       </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="5" t="n">
         <v>4.402140918023255</v>
       </c>
-      <c r="G158" s="8" t="n">
+      <c r="G158" s="9" t="n">
         <v>0.7248062015503876</v>
       </c>
       <c r="H158" s="3" t="n">
@@ -8072,13 +8653,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E159" s="7" t="n">
+      <c r="E159" s="4" t="n">
         <v>2196</v>
       </c>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="5" t="n">
         <v>4.401176383424408</v>
       </c>
-      <c r="G159" s="8" t="n">
+      <c r="G159" s="9" t="n">
         <v>0.7167577413479053</v>
       </c>
       <c r="H159" s="3" t="n">
@@ -8104,13 +8685,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E160" s="7" t="n">
+      <c r="E160" s="4" t="n">
         <v>2028</v>
       </c>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="5" t="n">
         <v>4.396591067061144</v>
       </c>
-      <c r="G160" s="8" t="n">
+      <c r="G160" s="9" t="n">
         <v>0.7327416173570019</v>
       </c>
       <c r="H160" s="3" t="n">
@@ -8136,13 +8717,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E161" s="7" t="n">
+      <c r="E161" s="4" t="n">
         <v>1442</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="5" t="n">
         <v>4.393987012690707</v>
       </c>
-      <c r="G161" s="8" t="n">
+      <c r="G161" s="9" t="n">
         <v>0.7212205270457698</v>
       </c>
       <c r="H161" s="3" t="n">
@@ -8168,13 +8749,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E162" s="7" t="n">
+      <c r="E162" s="4" t="n">
         <v>1230</v>
       </c>
-      <c r="F162" s="4" t="n">
+      <c r="F162" s="5" t="n">
         <v>4.381312269918698</v>
       </c>
-      <c r="G162" s="8" t="n">
+      <c r="G162" s="9" t="n">
         <v>0.748780487804878</v>
       </c>
       <c r="H162" s="3" t="n">
@@ -8200,13 +8781,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E163" s="7" t="n">
+      <c r="E163" s="4" t="n">
         <v>7142</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="5" t="n">
         <v>4.372930629025484</v>
       </c>
-      <c r="G163" s="8" t="n">
+      <c r="G163" s="9" t="n">
         <v>0.7300476057126856</v>
       </c>
       <c r="H163" s="3" t="n">
@@ -8232,13 +8813,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E164" s="7" t="n">
+      <c r="E164" s="4" t="n">
         <v>4472</v>
       </c>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="5" t="n">
         <v>4.370846053555456</v>
       </c>
-      <c r="G164" s="8" t="n">
+      <c r="G164" s="9" t="n">
         <v>0.7151162790697675</v>
       </c>
       <c r="H164" s="3" t="n">
@@ -8264,13 +8845,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E165" s="7" t="n">
+      <c r="E165" s="4" t="n">
         <v>855</v>
       </c>
-      <c r="F165" s="4" t="n">
+      <c r="F165" s="5" t="n">
         <v>4.35568606502924</v>
       </c>
-      <c r="G165" s="8" t="n">
+      <c r="G165" s="9" t="n">
         <v>0.6842105263157895</v>
       </c>
       <c r="H165" s="3" t="n">
@@ -8296,13 +8877,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E166" s="7" t="n">
+      <c r="E166" s="4" t="n">
         <v>1367</v>
       </c>
-      <c r="F166" s="4" t="n">
+      <c r="F166" s="5" t="n">
         <v>4.352846499341624</v>
       </c>
-      <c r="G166" s="8" t="n">
+      <c r="G166" s="9" t="n">
         <v>0.681784930504755</v>
       </c>
       <c r="H166" s="3" t="n">
@@ -8328,13 +8909,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E167" s="7" t="n">
+      <c r="E167" s="4" t="n">
         <v>8442</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="5" t="n">
         <v>4.350888400781804</v>
       </c>
-      <c r="G167" s="8" t="n">
+      <c r="G167" s="9" t="n">
         <v>0.7004264392324094</v>
       </c>
       <c r="H167" s="3" t="n">
@@ -8360,13 +8941,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E168" s="7" t="n">
+      <c r="E168" s="4" t="n">
         <v>2751</v>
       </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="5" t="n">
         <v>4.349907293929479</v>
       </c>
-      <c r="G168" s="8" t="n">
+      <c r="G168" s="9" t="n">
         <v>0.7273718647764449</v>
       </c>
       <c r="H168" s="3" t="n">
@@ -8392,13 +8973,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E169" s="7" t="n">
+      <c r="E169" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="5" t="n">
         <v>4.330204934366064</v>
       </c>
-      <c r="G169" s="8" t="n">
+      <c r="G169" s="9" t="n">
         <v>0.6901811248808389</v>
       </c>
       <c r="H169" s="3" t="n">
@@ -8424,13 +9005,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E170" s="7" t="n">
+      <c r="E170" s="4" t="n">
         <v>3482</v>
       </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="5" t="n">
         <v>4.32311627007467</v>
       </c>
-      <c r="G170" s="8" t="n">
+      <c r="G170" s="9" t="n">
         <v>0.7107983917288915</v>
       </c>
       <c r="H170" s="3" t="n">
@@ -8456,13 +9037,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E171" s="7" t="n">
+      <c r="E171" s="4" t="n">
         <v>2997</v>
       </c>
-      <c r="F171" s="4" t="n">
+      <c r="F171" s="5" t="n">
         <v>4.30302725005005</v>
       </c>
-      <c r="G171" s="8" t="n">
+      <c r="G171" s="9" t="n">
         <v>0.7380714047380714</v>
       </c>
       <c r="H171" s="3" t="n">
@@ -8488,13 +9069,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E172" s="7" t="n">
+      <c r="E172" s="4" t="n">
         <v>1026</v>
       </c>
-      <c r="F172" s="4" t="n">
+      <c r="F172" s="5" t="n">
         <v>4.299579282846004</v>
       </c>
-      <c r="G172" s="8" t="n">
+      <c r="G172" s="9" t="n">
         <v>0.7339181286549707</v>
       </c>
       <c r="H172" s="3" t="n">
@@ -8520,13 +9101,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E173" s="7" t="n">
+      <c r="E173" s="4" t="n">
         <v>1008</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="5" t="n">
         <v>4.296607547619048</v>
       </c>
-      <c r="G173" s="8" t="n">
+      <c r="G173" s="9" t="n">
         <v>0.7103174603174603</v>
       </c>
       <c r="H173" s="3" t="n">
@@ -8552,13 +9133,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E174" s="7" t="n">
+      <c r="E174" s="4" t="n">
         <v>2279</v>
       </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="5" t="n">
         <v>4.290566402544975</v>
       </c>
-      <c r="G174" s="8" t="n">
+      <c r="G174" s="9" t="n">
         <v>0.7959631417288284</v>
       </c>
       <c r="H174" s="3" t="n">
@@ -8584,13 +9165,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E175" s="7" t="n">
+      <c r="E175" s="4" t="n">
         <v>1131</v>
       </c>
-      <c r="F175" s="4" t="n">
+      <c r="F175" s="5" t="n">
         <v>4.276568426171529</v>
       </c>
-      <c r="G175" s="8" t="n">
+      <c r="G175" s="9" t="n">
         <v>0.6648983200707339</v>
       </c>
       <c r="H175" s="3" t="n">
@@ -8616,13 +9197,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E176" s="7" t="n">
+      <c r="E176" s="4" t="n">
         <v>4470</v>
       </c>
-      <c r="F176" s="4" t="n">
+      <c r="F176" s="5" t="n">
         <v>4.264221302483222</v>
       </c>
-      <c r="G176" s="8" t="n">
+      <c r="G176" s="9" t="n">
         <v>0.6378076062639821</v>
       </c>
       <c r="H176" s="3" t="n">
@@ -8648,13 +9229,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E177" s="7" t="n">
+      <c r="E177" s="4" t="n">
         <v>2275</v>
       </c>
-      <c r="F177" s="4" t="n">
+      <c r="F177" s="5" t="n">
         <v>4.261370309538462</v>
       </c>
-      <c r="G177" s="8" t="n">
+      <c r="G177" s="9" t="n">
         <v>0.6892307692307692</v>
       </c>
       <c r="H177" s="3" t="n">
@@ -8680,13 +9261,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E178" s="7" t="n">
+      <c r="E178" s="4" t="n">
         <v>1003</v>
       </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="5" t="n">
         <v>4.242015751345962</v>
       </c>
-      <c r="G178" s="8" t="n">
+      <c r="G178" s="9" t="n">
         <v>0.7018943170488534</v>
       </c>
       <c r="H178" s="3" t="n">
@@ -8712,13 +9293,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E179" s="7" t="n">
+      <c r="E179" s="4" t="n">
         <v>3388</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="F179" s="5" t="n">
         <v>4.224237</v>
       </c>
-      <c r="G179" s="8" t="n">
+      <c r="G179" s="9" t="n">
         <v>0.6688311688311688</v>
       </c>
       <c r="H179" s="3" t="n">
@@ -8744,13 +9325,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E180" s="7" t="n">
+      <c r="E180" s="4" t="n">
         <v>8034</v>
       </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" s="5" t="n">
         <v>4.214265260393328</v>
       </c>
-      <c r="G180" s="8" t="n">
+      <c r="G180" s="9" t="n">
         <v>0.7165795369678865</v>
       </c>
       <c r="H180" s="3" t="n">
@@ -8776,13 +9357,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E181" s="7" t="n">
+      <c r="E181" s="4" t="n">
         <v>7328</v>
       </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="5" t="n">
         <v>4.210234791157205</v>
       </c>
-      <c r="G181" s="8" t="n">
+      <c r="G181" s="9" t="n">
         <v>0.5930676855895196</v>
       </c>
       <c r="H181" s="3" t="n">
@@ -8808,13 +9389,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E182" s="7" t="n">
+      <c r="E182" s="4" t="n">
         <v>3863</v>
       </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="5" t="n">
         <v>4.207047383743205</v>
       </c>
-      <c r="G182" s="8" t="n">
+      <c r="G182" s="9" t="n">
         <v>0.6893606005695055</v>
       </c>
       <c r="H182" s="3" t="n">
@@ -8840,13 +9421,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E183" s="7" t="n">
+      <c r="E183" s="4" t="n">
         <v>1841</v>
       </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="5" t="n">
         <v>4.179237044486692</v>
       </c>
-      <c r="G183" s="8" t="n">
+      <c r="G183" s="9" t="n">
         <v>0.6230309614340033</v>
       </c>
       <c r="H183" s="3" t="n">
@@ -8872,13 +9453,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E184" s="7" t="n">
+      <c r="E184" s="4" t="n">
         <v>782</v>
       </c>
-      <c r="F184" s="4" t="n">
+      <c r="F184" s="5" t="n">
         <v>4.17552008516624</v>
       </c>
-      <c r="G184" s="8" t="n">
+      <c r="G184" s="9" t="n">
         <v>0.7480818414322251</v>
       </c>
       <c r="H184" s="3" t="n">
@@ -8904,13 +9485,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E185" s="7" t="n">
+      <c r="E185" s="4" t="n">
         <v>5645</v>
       </c>
-      <c r="F185" s="4" t="n">
+      <c r="F185" s="5" t="n">
         <v>4.173181913782107</v>
       </c>
-      <c r="G185" s="8" t="n">
+      <c r="G185" s="9" t="n">
         <v>0.7257750221434898</v>
       </c>
       <c r="H185" s="3" t="n">
@@ -8936,13 +9517,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E186" s="7" t="n">
+      <c r="E186" s="4" t="n">
         <v>25482</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="F186" s="5" t="n">
         <v>4.148704144227298</v>
       </c>
-      <c r="G186" s="8" t="n">
+      <c r="G186" s="9" t="n">
         <v>0.7561023467545719</v>
       </c>
       <c r="H186" s="3" t="n">
@@ -8968,13 +9549,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E187" s="7" t="n">
+      <c r="E187" s="4" t="n">
         <v>7653</v>
       </c>
-      <c r="F187" s="4" t="n">
+      <c r="F187" s="5" t="n">
         <v>4.143697301816282</v>
       </c>
-      <c r="G187" s="8" t="n">
+      <c r="G187" s="9" t="n">
         <v>0.6828694629557036</v>
       </c>
       <c r="H187" s="3" t="n">
@@ -8996,13 +9577,13 @@
         </is>
       </c>
       <c r="D188" s="3" t="n"/>
-      <c r="E188" s="7" t="n">
+      <c r="E188" s="4" t="n">
         <v>5516</v>
       </c>
-      <c r="F188" s="4" t="n">
+      <c r="F188" s="5" t="n">
         <v>4.139340412146483</v>
       </c>
-      <c r="G188" s="8" t="n">
+      <c r="G188" s="9" t="n">
         <v>0.5398839738941261</v>
       </c>
       <c r="H188" s="3" t="n">
@@ -9028,13 +9609,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E189" s="7" t="n">
+      <c r="E189" s="4" t="n">
         <v>604</v>
       </c>
-      <c r="F189" s="4" t="n">
+      <c r="F189" s="5" t="n">
         <v>4.132568207781457</v>
       </c>
-      <c r="G189" s="8" t="n">
+      <c r="G189" s="9" t="n">
         <v>0.6556291390728477</v>
       </c>
       <c r="H189" s="3" t="n">
@@ -9060,13 +9641,13 @@
           <t>Dopa</t>
         </is>
       </c>
-      <c r="E190" s="7" t="n">
+      <c r="E190" s="4" t="n">
         <v>4239</v>
       </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="5" t="n">
         <v>4.119035481410711</v>
       </c>
-      <c r="G190" s="8" t="n">
+      <c r="G190" s="9" t="n">
         <v>0.7395612172682237</v>
       </c>
       <c r="H190" s="3" t="n">
@@ -9092,13 +9673,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E191" s="7" t="n">
+      <c r="E191" s="4" t="n">
         <v>4562</v>
       </c>
-      <c r="F191" s="4" t="n">
+      <c r="F191" s="5" t="n">
         <v>4.098648341473038</v>
       </c>
-      <c r="G191" s="8" t="n">
+      <c r="G191" s="9" t="n">
         <v>0.6790881192459448</v>
       </c>
       <c r="H191" s="3" t="n">
@@ -9124,13 +9705,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E192" s="7" t="n">
+      <c r="E192" s="4" t="n">
         <v>3054</v>
       </c>
-      <c r="F192" s="4" t="n">
+      <c r="F192" s="5" t="n">
         <v>4.091216022888015</v>
       </c>
-      <c r="G192" s="8" t="n">
+      <c r="G192" s="9" t="n">
         <v>0.6889325474787165</v>
       </c>
       <c r="H192" s="3" t="n">
@@ -9152,13 +9733,13 @@
         </is>
       </c>
       <c r="D193" s="3" t="n"/>
-      <c r="E193" s="7" t="n">
+      <c r="E193" s="4" t="n">
         <v>139030</v>
       </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="5" t="n">
         <v>4.086697386960369</v>
       </c>
-      <c r="G193" s="8" t="n">
+      <c r="G193" s="9" t="n">
         <v>0.5374955045673596</v>
       </c>
       <c r="H193" s="3" t="n">
@@ -9184,13 +9765,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E194" s="7" t="n">
+      <c r="E194" s="4" t="n">
         <v>2465</v>
       </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="5" t="n">
         <v>4.068364575212982</v>
       </c>
-      <c r="G194" s="8" t="n">
+      <c r="G194" s="9" t="n">
         <v>0.7330628803245436</v>
       </c>
       <c r="H194" s="3" t="n">
@@ -9216,13 +9797,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E195" s="7" t="n">
+      <c r="E195" s="4" t="n">
         <v>1378</v>
       </c>
-      <c r="F195" s="4" t="n">
+      <c r="F195" s="5" t="n">
         <v>4.065678225544268</v>
       </c>
-      <c r="G195" s="8" t="n">
+      <c r="G195" s="9" t="n">
         <v>0.6698113207547169</v>
       </c>
       <c r="H195" s="3" t="n">
@@ -9248,13 +9829,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E196" s="7" t="n">
+      <c r="E196" s="4" t="n">
         <v>2043</v>
       </c>
-      <c r="F196" s="4" t="n">
+      <c r="F196" s="5" t="n">
         <v>3.950236508761625</v>
       </c>
-      <c r="G196" s="8" t="n">
+      <c r="G196" s="9" t="n">
         <v>0.6319138521781693</v>
       </c>
       <c r="H196" s="3" t="n">
@@ -9280,13 +9861,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E197" s="7" t="n">
+      <c r="E197" s="4" t="n">
         <v>1211</v>
       </c>
-      <c r="F197" s="4" t="n">
+      <c r="F197" s="5" t="n">
         <v>3.938929703798513</v>
       </c>
-      <c r="G197" s="8" t="n">
+      <c r="G197" s="9" t="n">
         <v>0.7060280759702725</v>
       </c>
       <c r="H197" s="3" t="n">
@@ -9308,13 +9889,13 @@
         </is>
       </c>
       <c r="D198" s="3" t="n"/>
-      <c r="E198" s="7" t="n">
+      <c r="E198" s="4" t="n">
         <v>699</v>
       </c>
-      <c r="F198" s="4" t="n">
+      <c r="F198" s="5" t="n">
         <v>3.935627006151646</v>
       </c>
-      <c r="G198" s="8" t="n">
+      <c r="G198" s="9" t="n">
         <v>0.530758226037196</v>
       </c>
       <c r="H198" s="3" t="n">
@@ -9340,13 +9921,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E199" s="7" t="n">
+      <c r="E199" s="4" t="n">
         <v>3955</v>
       </c>
-      <c r="F199" s="4" t="n">
+      <c r="F199" s="5" t="n">
         <v>3.903761504879899</v>
       </c>
-      <c r="G199" s="8" t="n">
+      <c r="G199" s="9" t="n">
         <v>0.6558786346396965</v>
       </c>
       <c r="H199" s="3" t="n">
@@ -9372,13 +9953,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E200" s="7" t="n">
+      <c r="E200" s="4" t="n">
         <v>1106</v>
       </c>
-      <c r="F200" s="4" t="n">
+      <c r="F200" s="5" t="n">
         <v>3.893269672694395</v>
       </c>
-      <c r="G200" s="8" t="n">
+      <c r="G200" s="9" t="n">
         <v>0.6672694394213382</v>
       </c>
       <c r="H200" s="3" t="n">
@@ -9400,13 +9981,13 @@
         </is>
       </c>
       <c r="D201" s="3" t="n"/>
-      <c r="E201" s="7" t="n">
+      <c r="E201" s="4" t="n">
         <v>81472</v>
       </c>
-      <c r="F201" s="4" t="n">
+      <c r="F201" s="5" t="n">
         <v>3.879017706744648</v>
       </c>
-      <c r="G201" s="8" t="n">
+      <c r="G201" s="9" t="n">
         <v>0.4917272191673212</v>
       </c>
       <c r="H201" s="3" t="n">
@@ -9432,13 +10013,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E202" s="7" t="n">
+      <c r="E202" s="4" t="n">
         <v>874</v>
       </c>
-      <c r="F202" s="4" t="n">
+      <c r="F202" s="5" t="n">
         <v>3.872903893707094</v>
       </c>
-      <c r="G202" s="8" t="n">
+      <c r="G202" s="9" t="n">
         <v>0.7013729977116705</v>
       </c>
       <c r="H202" s="3" t="n">
@@ -9464,13 +10045,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E203" s="7" t="n">
+      <c r="E203" s="4" t="n">
         <v>1945</v>
       </c>
-      <c r="F203" s="4" t="n">
+      <c r="F203" s="5" t="n">
         <v>3.871827307249358</v>
       </c>
-      <c r="G203" s="8" t="n">
+      <c r="G203" s="9" t="n">
         <v>0.5820051413881748</v>
       </c>
       <c r="H203" s="3" t="n">
@@ -9496,13 +10077,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E204" s="7" t="n">
+      <c r="E204" s="4" t="n">
         <v>6222</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="F204" s="5" t="n">
         <v>3.862999672356156</v>
       </c>
-      <c r="G204" s="8" t="n">
+      <c r="G204" s="9" t="n">
         <v>0.635326261652202</v>
       </c>
       <c r="H204" s="3" t="n">
@@ -9528,13 +10109,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E205" s="7" t="n">
+      <c r="E205" s="4" t="n">
         <v>1544</v>
       </c>
-      <c r="F205" s="4" t="n">
+      <c r="F205" s="5" t="n">
         <v>3.861328956735752</v>
       </c>
-      <c r="G205" s="8" t="n">
+      <c r="G205" s="9" t="n">
         <v>0.6405440414507771</v>
       </c>
       <c r="H205" s="3" t="n">
@@ -9560,13 +10141,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E206" s="7" t="n">
+      <c r="E206" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="F206" s="4" t="n">
+      <c r="F206" s="5" t="n">
         <v>3.844974230316742</v>
       </c>
-      <c r="G206" s="8" t="n">
+      <c r="G206" s="9" t="n">
         <v>0.6556561085972851</v>
       </c>
       <c r="H206" s="3" t="n">
@@ -9592,13 +10173,13 @@
           <t>GABA-Glyc</t>
         </is>
       </c>
-      <c r="E207" s="7" t="n">
+      <c r="E207" s="4" t="n">
         <v>1582</v>
       </c>
-      <c r="F207" s="4" t="n">
+      <c r="F207" s="5" t="n">
         <v>3.8420627</v>
       </c>
-      <c r="G207" s="8" t="n">
+      <c r="G207" s="9" t="n">
         <v>0.6536030341340076</v>
       </c>
       <c r="H207" s="3" t="n">
@@ -9624,13 +10205,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E208" s="7" t="n">
+      <c r="E208" s="4" t="n">
         <v>8756</v>
       </c>
-      <c r="F208" s="4" t="n">
+      <c r="F208" s="5" t="n">
         <v>3.80938973457058</v>
       </c>
-      <c r="G208" s="8" t="n">
+      <c r="G208" s="9" t="n">
         <v>0.6740520785746916</v>
       </c>
       <c r="H208" s="3" t="n">
@@ -9652,13 +10233,13 @@
         </is>
       </c>
       <c r="D209" s="3" t="n"/>
-      <c r="E209" s="7" t="n">
+      <c r="E209" s="4" t="n">
         <v>84356</v>
       </c>
-      <c r="F209" s="4" t="n">
+      <c r="F209" s="5" t="n">
         <v>3.790201947700223</v>
       </c>
-      <c r="G209" s="8" t="n">
+      <c r="G209" s="9" t="n">
         <v>0.4937763763099246</v>
       </c>
       <c r="H209" s="3" t="n">
@@ -9684,13 +10265,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E210" s="7" t="n">
+      <c r="E210" s="4" t="n">
         <v>8782</v>
       </c>
-      <c r="F210" s="4" t="n">
+      <c r="F210" s="5" t="n">
         <v>3.778066588499203</v>
       </c>
-      <c r="G210" s="8" t="n">
+      <c r="G210" s="9" t="n">
         <v>0.632316101115919</v>
       </c>
       <c r="H210" s="3" t="n">
@@ -9712,13 +10293,13 @@
         </is>
       </c>
       <c r="D211" s="3" t="n"/>
-      <c r="E211" s="7" t="n">
+      <c r="E211" s="4" t="n">
         <v>144668</v>
       </c>
-      <c r="F211" s="4" t="n">
+      <c r="F211" s="5" t="n">
         <v>3.772723433937706</v>
       </c>
-      <c r="G211" s="8" t="n">
+      <c r="G211" s="9" t="n">
         <v>0.5096496806481047</v>
       </c>
       <c r="H211" s="3" t="n">
@@ -9744,13 +10325,13 @@
           <t>Chol</t>
         </is>
       </c>
-      <c r="E212" s="7" t="n">
+      <c r="E212" s="4" t="n">
         <v>1190</v>
       </c>
-      <c r="F212" s="4" t="n">
+      <c r="F212" s="5" t="n">
         <v>3.755416682016807</v>
       </c>
-      <c r="G212" s="8" t="n">
+      <c r="G212" s="9" t="n">
         <v>0.6873949579831933</v>
       </c>
       <c r="H212" s="3" t="n">
@@ -9776,13 +10357,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E213" s="7" t="n">
+      <c r="E213" s="4" t="n">
         <v>1511</v>
       </c>
-      <c r="F213" s="4" t="n">
+      <c r="F213" s="5" t="n">
         <v>3.709584064063534</v>
       </c>
-      <c r="G213" s="8" t="n">
+      <c r="G213" s="9" t="n">
         <v>0.6168100595632032</v>
       </c>
       <c r="H213" s="3" t="n">
@@ -9808,13 +10389,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E214" s="7" t="n">
+      <c r="E214" s="4" t="n">
         <v>2201</v>
       </c>
-      <c r="F214" s="4" t="n">
+      <c r="F214" s="5" t="n">
         <v>3.701608878464335</v>
       </c>
-      <c r="G214" s="8" t="n">
+      <c r="G214" s="9" t="n">
         <v>0.660154475238528</v>
       </c>
       <c r="H214" s="3" t="n">
@@ -9840,13 +10421,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E215" s="7" t="n">
+      <c r="E215" s="4" t="n">
         <v>1542</v>
       </c>
-      <c r="F215" s="4" t="n">
+      <c r="F215" s="5" t="n">
         <v>3.685396268223086</v>
       </c>
-      <c r="G215" s="8" t="n">
+      <c r="G215" s="9" t="n">
         <v>0.6167315175097277</v>
       </c>
       <c r="H215" s="3" t="n">
@@ -9872,13 +10453,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E216" s="7" t="n">
+      <c r="E216" s="4" t="n">
         <v>6921</v>
       </c>
-      <c r="F216" s="4" t="n">
+      <c r="F216" s="5" t="n">
         <v>3.678539518638925</v>
       </c>
-      <c r="G216" s="8" t="n">
+      <c r="G216" s="9" t="n">
         <v>0.6808264701632712</v>
       </c>
       <c r="H216" s="3" t="n">
@@ -9904,13 +10485,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E217" s="7" t="n">
+      <c r="E217" s="4" t="n">
         <v>1868</v>
       </c>
-      <c r="F217" s="4" t="n">
+      <c r="F217" s="5" t="n">
         <v>3.659986808297645</v>
       </c>
-      <c r="G217" s="8" t="n">
+      <c r="G217" s="9" t="n">
         <v>0.7135974304068522</v>
       </c>
       <c r="H217" s="3" t="n">
@@ -9936,13 +10517,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E218" s="7" t="n">
+      <c r="E218" s="4" t="n">
         <v>19786</v>
       </c>
-      <c r="F218" s="4" t="n">
+      <c r="F218" s="5" t="n">
         <v>3.659825473804711</v>
       </c>
-      <c r="G218" s="8" t="n">
+      <c r="G218" s="9" t="n">
         <v>0.5959769534013948</v>
       </c>
       <c r="H218" s="3" t="n">
@@ -9964,13 +10545,13 @@
         </is>
       </c>
       <c r="D219" s="3" t="n"/>
-      <c r="E219" s="7" t="n">
+      <c r="E219" s="4" t="n">
         <v>1487</v>
       </c>
-      <c r="F219" s="4" t="n">
+      <c r="F219" s="5" t="n">
         <v>3.658249380901144</v>
       </c>
-      <c r="G219" s="8" t="n">
+      <c r="G219" s="9" t="n">
         <v>0.5097511768661735</v>
       </c>
       <c r="H219" s="3" t="n">
@@ -9996,13 +10577,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E220" s="7" t="n">
+      <c r="E220" s="4" t="n">
         <v>10165</v>
       </c>
-      <c r="F220" s="4" t="n">
+      <c r="F220" s="5" t="n">
         <v>3.642240665863256</v>
       </c>
-      <c r="G220" s="8" t="n">
+      <c r="G220" s="9" t="n">
         <v>0.6520413182488932</v>
       </c>
       <c r="H220" s="3" t="n">
@@ -10028,13 +10609,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E221" s="7" t="n">
+      <c r="E221" s="4" t="n">
         <v>3956</v>
       </c>
-      <c r="F221" s="4" t="n">
+      <c r="F221" s="5" t="n">
         <v>3.613794516506573</v>
       </c>
-      <c r="G221" s="8" t="n">
+      <c r="G221" s="9" t="n">
         <v>0.5755813953488372</v>
       </c>
       <c r="H221" s="3" t="n">
@@ -10060,13 +10641,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E222" s="7" t="n">
+      <c r="E222" s="4" t="n">
         <v>1873</v>
       </c>
-      <c r="F222" s="4" t="n">
+      <c r="F222" s="5" t="n">
         <v>3.61019692648158</v>
       </c>
-      <c r="G222" s="8" t="n">
+      <c r="G222" s="9" t="n">
         <v>0.611318739989322</v>
       </c>
       <c r="H222" s="3" t="n">
@@ -10088,13 +10669,13 @@
         </is>
       </c>
       <c r="D223" s="3" t="n"/>
-      <c r="E223" s="7" t="n">
+      <c r="E223" s="4" t="n">
         <v>3321</v>
       </c>
-      <c r="F223" s="4" t="n">
+      <c r="F223" s="5" t="n">
         <v>3.606476154080097</v>
       </c>
-      <c r="G223" s="8" t="n">
+      <c r="G223" s="9" t="n">
         <v>0.5323697681421259</v>
       </c>
       <c r="H223" s="3" t="n">
@@ -10120,13 +10701,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E224" s="7" t="n">
+      <c r="E224" s="4" t="n">
         <v>2344</v>
       </c>
-      <c r="F224" s="4" t="n">
+      <c r="F224" s="5" t="n">
         <v>3.601606449530717</v>
       </c>
-      <c r="G224" s="8" t="n">
+      <c r="G224" s="9" t="n">
         <v>0.6749146757679181</v>
       </c>
       <c r="H224" s="3" t="n">
@@ -10152,13 +10733,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E225" s="7" t="n">
+      <c r="E225" s="4" t="n">
         <v>861</v>
       </c>
-      <c r="F225" s="4" t="n">
+      <c r="F225" s="5" t="n">
         <v>3.596563016027874</v>
       </c>
-      <c r="G225" s="8" t="n">
+      <c r="G225" s="9" t="n">
         <v>0.6225319396051103</v>
       </c>
       <c r="H225" s="3" t="n">
@@ -10184,13 +10765,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E226" s="7" t="n">
+      <c r="E226" s="4" t="n">
         <v>952</v>
       </c>
-      <c r="F226" s="4" t="n">
+      <c r="F226" s="5" t="n">
         <v>3.572296491386555</v>
       </c>
-      <c r="G226" s="8" t="n">
+      <c r="G226" s="9" t="n">
         <v>0.6060924369747899</v>
       </c>
       <c r="H226" s="3" t="n">
@@ -10216,13 +10797,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E227" s="7" t="n">
+      <c r="E227" s="4" t="n">
         <v>889</v>
       </c>
-      <c r="F227" s="4" t="n">
+      <c r="F227" s="5" t="n">
         <v>3.567711175815523</v>
       </c>
-      <c r="G227" s="8" t="n">
+      <c r="G227" s="9" t="n">
         <v>0.5995500562429696</v>
       </c>
       <c r="H227" s="3" t="n">
@@ -10248,13 +10829,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E228" s="7" t="n">
+      <c r="E228" s="4" t="n">
         <v>35689</v>
       </c>
-      <c r="F228" s="4" t="n">
+      <c r="F228" s="5" t="n">
         <v>3.560319167639889</v>
       </c>
-      <c r="G228" s="8" t="n">
+      <c r="G228" s="9" t="n">
         <v>0.6155678220179888</v>
       </c>
       <c r="H228" s="3" t="n">
@@ -10280,13 +10861,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E229" s="7" t="n">
+      <c r="E229" s="4" t="n">
         <v>15973</v>
       </c>
-      <c r="F229" s="4" t="n">
+      <c r="F229" s="5" t="n">
         <v>3.527928914167658</v>
       </c>
-      <c r="G229" s="8" t="n">
+      <c r="G229" s="9" t="n">
         <v>0.6288111187629124</v>
       </c>
       <c r="H229" s="3" t="n">
@@ -10312,13 +10893,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E230" s="7" t="n">
+      <c r="E230" s="4" t="n">
         <v>1206</v>
       </c>
-      <c r="F230" s="4" t="n">
+      <c r="F230" s="5" t="n">
         <v>3.50889340854063</v>
       </c>
-      <c r="G230" s="8" t="n">
+      <c r="G230" s="9" t="n">
         <v>0.6243781094527363</v>
       </c>
       <c r="H230" s="3" t="n">
@@ -10344,13 +10925,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E231" s="7" t="n">
+      <c r="E231" s="4" t="n">
         <v>31619</v>
       </c>
-      <c r="F231" s="4" t="n">
+      <c r="F231" s="5" t="n">
         <v>3.504228716069452</v>
       </c>
-      <c r="G231" s="8" t="n">
+      <c r="G231" s="9" t="n">
         <v>0.5190549985768049</v>
       </c>
       <c r="H231" s="3" t="n">
@@ -10376,13 +10957,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E232" s="7" t="n">
+      <c r="E232" s="4" t="n">
         <v>1386</v>
       </c>
-      <c r="F232" s="4" t="n">
+      <c r="F232" s="5" t="n">
         <v>3.46603611038961</v>
       </c>
-      <c r="G232" s="8" t="n">
+      <c r="G232" s="9" t="n">
         <v>0.6067821067821068</v>
       </c>
       <c r="H232" s="3" t="n">
@@ -10408,13 +10989,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E233" s="7" t="n">
+      <c r="E233" s="4" t="n">
         <v>1169</v>
       </c>
-      <c r="F233" s="4" t="n">
+      <c r="F233" s="5" t="n">
         <v>3.462178700684345</v>
       </c>
-      <c r="G233" s="8" t="n">
+      <c r="G233" s="9" t="n">
         <v>0.5431993156544055</v>
       </c>
       <c r="H233" s="3" t="n">
@@ -10440,13 +11021,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E234" s="7" t="n">
+      <c r="E234" s="4" t="n">
         <v>5727</v>
       </c>
-      <c r="F234" s="4" t="n">
+      <c r="F234" s="5" t="n">
         <v>3.456922493277458</v>
       </c>
-      <c r="G234" s="8" t="n">
+      <c r="G234" s="9" t="n">
         <v>0.5816308713113323</v>
       </c>
       <c r="H234" s="3" t="n">
@@ -10472,13 +11053,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E235" s="7" t="n">
+      <c r="E235" s="4" t="n">
         <v>7117</v>
       </c>
-      <c r="F235" s="4" t="n">
+      <c r="F235" s="5" t="n">
         <v>3.453152280694113</v>
       </c>
-      <c r="G235" s="8" t="n">
+      <c r="G235" s="9" t="n">
         <v>0.5692005058311086</v>
       </c>
       <c r="H235" s="3" t="n">
@@ -10504,13 +11085,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E236" s="7" t="n">
+      <c r="E236" s="4" t="n">
         <v>3172</v>
       </c>
-      <c r="F236" s="4" t="n">
+      <c r="F236" s="5" t="n">
         <v>3.434881423203026</v>
       </c>
-      <c r="G236" s="8" t="n">
+      <c r="G236" s="9" t="n">
         <v>0.6727616645649432</v>
       </c>
       <c r="H236" s="3" t="n">
@@ -10536,13 +11117,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E237" s="7" t="n">
+      <c r="E237" s="4" t="n">
         <v>1807</v>
       </c>
-      <c r="F237" s="4" t="n">
+      <c r="F237" s="5" t="n">
         <v>3.4340034</v>
       </c>
-      <c r="G237" s="8" t="n">
+      <c r="G237" s="9" t="n">
         <v>0.6347537354731599</v>
       </c>
       <c r="H237" s="3" t="n">
@@ -10564,13 +11145,13 @@
         </is>
       </c>
       <c r="D238" s="3" t="n"/>
-      <c r="E238" s="7" t="n">
+      <c r="E238" s="4" t="n">
         <v>8544</v>
       </c>
-      <c r="F238" s="4" t="n">
+      <c r="F238" s="5" t="n">
         <v>3.433970357876873</v>
       </c>
-      <c r="G238" s="8" t="n">
+      <c r="G238" s="9" t="n">
         <v>0.4590355805243445</v>
       </c>
       <c r="H238" s="3" t="n">
@@ -10592,13 +11173,13 @@
         </is>
       </c>
       <c r="D239" s="3" t="n"/>
-      <c r="E239" s="7" t="n">
+      <c r="E239" s="4" t="n">
         <v>3096</v>
       </c>
-      <c r="F239" s="4" t="n">
+      <c r="F239" s="5" t="n">
         <v>3.430613374515504</v>
       </c>
-      <c r="G239" s="8" t="n">
+      <c r="G239" s="9" t="n">
         <v>0.5051679586563307</v>
       </c>
       <c r="H239" s="3" t="n">
@@ -10624,13 +11205,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E240" s="7" t="n">
+      <c r="E240" s="4" t="n">
         <v>6588</v>
       </c>
-      <c r="F240" s="4" t="n">
+      <c r="F240" s="5" t="n">
         <v>3.406108852276867</v>
       </c>
-      <c r="G240" s="8" t="n">
+      <c r="G240" s="9" t="n">
         <v>0.5769581056466302</v>
       </c>
       <c r="H240" s="3" t="n">
@@ -10656,13 +11237,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E241" s="7" t="n">
+      <c r="E241" s="4" t="n">
         <v>3620</v>
       </c>
-      <c r="F241" s="4" t="n">
+      <c r="F241" s="5" t="n">
         <v>3.38960661660221</v>
       </c>
-      <c r="G241" s="8" t="n">
+      <c r="G241" s="9" t="n">
         <v>0.6071823204419888</v>
       </c>
       <c r="H241" s="3" t="n">
@@ -10688,13 +11269,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E242" s="7" t="n">
+      <c r="E242" s="4" t="n">
         <v>14630</v>
       </c>
-      <c r="F242" s="4" t="n">
+      <c r="F242" s="5" t="n">
         <v>3.386445303636364</v>
       </c>
-      <c r="G242" s="8" t="n">
+      <c r="G242" s="9" t="n">
         <v>0.6435406698564593</v>
       </c>
       <c r="H242" s="3" t="n">
@@ -10720,13 +11301,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E243" s="7" t="n">
+      <c r="E243" s="4" t="n">
         <v>52484</v>
       </c>
-      <c r="F243" s="4" t="n">
+      <c r="F243" s="5" t="n">
         <v>3.375698774731346</v>
       </c>
-      <c r="G243" s="8" t="n">
+      <c r="G243" s="9" t="n">
         <v>0.5787287554302264</v>
       </c>
       <c r="H243" s="3" t="n">
@@ -10748,13 +11329,13 @@
         </is>
       </c>
       <c r="D244" s="3" t="n"/>
-      <c r="E244" s="7" t="n">
+      <c r="E244" s="4" t="n">
         <v>1715</v>
       </c>
-      <c r="F244" s="4" t="n">
+      <c r="F244" s="5" t="n">
         <v>3.353410260524781</v>
       </c>
-      <c r="G244" s="8" t="n">
+      <c r="G244" s="9" t="n">
         <v>0.4559766763848396</v>
       </c>
       <c r="H244" s="3" t="n">
@@ -10780,13 +11361,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E245" s="7" t="n">
+      <c r="E245" s="4" t="n">
         <v>2002</v>
       </c>
-      <c r="F245" s="4" t="n">
+      <c r="F245" s="5" t="n">
         <v>3.321107160139861</v>
       </c>
-      <c r="G245" s="8" t="n">
+      <c r="G245" s="9" t="n">
         <v>0.568931068931069</v>
       </c>
       <c r="H245" s="3" t="n">
@@ -10812,13 +11393,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E246" s="7" t="n">
+      <c r="E246" s="4" t="n">
         <v>2967</v>
       </c>
-      <c r="F246" s="4" t="n">
+      <c r="F246" s="5" t="n">
         <v>3.320926466430738</v>
       </c>
-      <c r="G246" s="8" t="n">
+      <c r="G246" s="9" t="n">
         <v>0.5551061678463095</v>
       </c>
       <c r="H246" s="3" t="n">
@@ -10844,13 +11425,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E247" s="7" t="n">
+      <c r="E247" s="4" t="n">
         <v>19939</v>
       </c>
-      <c r="F247" s="4" t="n">
+      <c r="F247" s="5" t="n">
         <v>3.281802428115753</v>
       </c>
-      <c r="G247" s="8" t="n">
+      <c r="G247" s="9" t="n">
         <v>0.5904007222027183</v>
       </c>
       <c r="H247" s="3" t="n">
@@ -10876,13 +11457,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E248" s="7" t="n">
+      <c r="E248" s="4" t="n">
         <v>1825</v>
       </c>
-      <c r="F248" s="4" t="n">
+      <c r="F248" s="5" t="n">
         <v>3.276859667780822</v>
       </c>
-      <c r="G248" s="8" t="n">
+      <c r="G248" s="9" t="n">
         <v>0.5698630136986301</v>
       </c>
       <c r="H248" s="3" t="n">
@@ -10908,13 +11489,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E249" s="7" t="n">
+      <c r="E249" s="4" t="n">
         <v>12315</v>
       </c>
-      <c r="F249" s="4" t="n">
+      <c r="F249" s="5" t="n">
         <v>3.263799585156313</v>
       </c>
-      <c r="G249" s="8" t="n">
+      <c r="G249" s="9" t="n">
         <v>0.4743808363784003</v>
       </c>
       <c r="H249" s="3" t="n">
@@ -10940,13 +11521,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E250" s="7" t="n">
+      <c r="E250" s="4" t="n">
         <v>8035</v>
       </c>
-      <c r="F250" s="4" t="n">
+      <c r="F250" s="5" t="n">
         <v>3.258880143223398</v>
       </c>
-      <c r="G250" s="8" t="n">
+      <c r="G250" s="9" t="n">
         <v>0.5607965152457997</v>
       </c>
       <c r="H250" s="3" t="n">
@@ -10972,13 +11553,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E251" s="7" t="n">
+      <c r="E251" s="4" t="n">
         <v>5393</v>
       </c>
-      <c r="F251" s="4" t="n">
+      <c r="F251" s="5" t="n">
         <v>3.25293879499351</v>
       </c>
-      <c r="G251" s="8" t="n">
+      <c r="G251" s="9" t="n">
         <v>0.5436677174114593</v>
       </c>
       <c r="H251" s="3" t="n">
@@ -11004,13 +11585,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E252" s="7" t="n">
+      <c r="E252" s="4" t="n">
         <v>1520</v>
       </c>
-      <c r="F252" s="4" t="n">
+      <c r="F252" s="5" t="n">
         <v>3.248060675855263</v>
       </c>
-      <c r="G252" s="8" t="n">
+      <c r="G252" s="9" t="n">
         <v>0.5638157894736842</v>
       </c>
       <c r="H252" s="3" t="n">
@@ -11036,13 +11617,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E253" s="7" t="n">
+      <c r="E253" s="4" t="n">
         <v>6060</v>
       </c>
-      <c r="F253" s="4" t="n">
+      <c r="F253" s="5" t="n">
         <v>3.240517314174917</v>
       </c>
-      <c r="G253" s="8" t="n">
+      <c r="G253" s="9" t="n">
         <v>0.6384488448844885</v>
       </c>
       <c r="H253" s="3" t="n">
@@ -11068,13 +11649,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E254" s="7" t="n">
+      <c r="E254" s="4" t="n">
         <v>827</v>
       </c>
-      <c r="F254" s="4" t="n">
+      <c r="F254" s="5" t="n">
         <v>3.20692332834341</v>
       </c>
-      <c r="G254" s="8" t="n">
+      <c r="G254" s="9" t="n">
         <v>0.5199516324062877</v>
       </c>
       <c r="H254" s="3" t="n">
@@ -11100,13 +11681,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E255" s="7" t="n">
+      <c r="E255" s="4" t="n">
         <v>7852</v>
       </c>
-      <c r="F255" s="4" t="n">
+      <c r="F255" s="5" t="n">
         <v>3.188968552852776</v>
       </c>
-      <c r="G255" s="8" t="n">
+      <c r="G255" s="9" t="n">
         <v>0.5323484462557311</v>
       </c>
       <c r="H255" s="3" t="n">
@@ -11132,13 +11713,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E256" s="7" t="n">
+      <c r="E256" s="4" t="n">
         <v>10367</v>
       </c>
-      <c r="F256" s="4" t="n">
+      <c r="F256" s="5" t="n">
         <v>3.157429369026719</v>
       </c>
-      <c r="G256" s="8" t="n">
+      <c r="G256" s="9" t="n">
         <v>0.5422012153950033</v>
       </c>
       <c r="H256" s="3" t="n">
@@ -11164,13 +11745,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E257" s="7" t="n">
+      <c r="E257" s="4" t="n">
         <v>5790</v>
       </c>
-      <c r="F257" s="4" t="n">
+      <c r="F257" s="5" t="n">
         <v>3.119684170569949</v>
       </c>
-      <c r="G257" s="8" t="n">
+      <c r="G257" s="9" t="n">
         <v>0.5392055267702937</v>
       </c>
       <c r="H257" s="3" t="n">
@@ -11196,13 +11777,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E258" s="7" t="n">
+      <c r="E258" s="4" t="n">
         <v>781</v>
       </c>
-      <c r="F258" s="4" t="n">
+      <c r="F258" s="5" t="n">
         <v>3.106317458898848</v>
       </c>
-      <c r="G258" s="8" t="n">
+      <c r="G258" s="9" t="n">
         <v>0.4788732394366197</v>
       </c>
       <c r="H258" s="3" t="n">
@@ -11228,13 +11809,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E259" s="7" t="n">
+      <c r="E259" s="4" t="n">
         <v>2840</v>
       </c>
-      <c r="F259" s="4" t="n">
+      <c r="F259" s="5" t="n">
         <v>3.101796407042253</v>
       </c>
-      <c r="G259" s="8" t="n">
+      <c r="G259" s="9" t="n">
         <v>0.6496478873239436</v>
       </c>
       <c r="H259" s="3" t="n">
@@ -11260,13 +11841,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E260" s="7" t="n">
+      <c r="E260" s="4" t="n">
         <v>537</v>
       </c>
-      <c r="F260" s="4" t="n">
+      <c r="F260" s="5" t="n">
         <v>3.089142017504656</v>
       </c>
-      <c r="G260" s="8" t="n">
+      <c r="G260" s="9" t="n">
         <v>0.5363128491620112</v>
       </c>
       <c r="H260" s="3" t="n">
@@ -11292,13 +11873,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E261" s="7" t="n">
+      <c r="E261" s="4" t="n">
         <v>1624</v>
       </c>
-      <c r="F261" s="4" t="n">
+      <c r="F261" s="5" t="n">
         <v>3.039610869150246</v>
       </c>
-      <c r="G261" s="8" t="n">
+      <c r="G261" s="9" t="n">
         <v>0.4193349753694581</v>
       </c>
       <c r="H261" s="3" t="n">
@@ -11320,13 +11901,13 @@
         </is>
       </c>
       <c r="D262" s="3" t="n"/>
-      <c r="E262" s="7" t="n">
+      <c r="E262" s="4" t="n">
         <v>1174</v>
       </c>
-      <c r="F262" s="4" t="n">
+      <c r="F262" s="5" t="n">
         <v>3.025557818279387</v>
       </c>
-      <c r="G262" s="8" t="n">
+      <c r="G262" s="9" t="n">
         <v>0.403747870528109</v>
       </c>
       <c r="H262" s="3" t="n">
@@ -11352,13 +11933,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E263" s="7" t="n">
+      <c r="E263" s="4" t="n">
         <v>4682</v>
       </c>
-      <c r="F263" s="4" t="n">
+      <c r="F263" s="5" t="n">
         <v>3.021389532635626</v>
       </c>
-      <c r="G263" s="8" t="n">
+      <c r="G263" s="9" t="n">
         <v>0.5435711234515165</v>
       </c>
       <c r="H263" s="3" t="n">
@@ -11384,13 +11965,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E264" s="7" t="n">
+      <c r="E264" s="4" t="n">
         <v>5327</v>
       </c>
-      <c r="F264" s="4" t="n">
+      <c r="F264" s="5" t="n">
         <v>3.021223289787873</v>
       </c>
-      <c r="G264" s="8" t="n">
+      <c r="G264" s="9" t="n">
         <v>0.5507790501220199</v>
       </c>
       <c r="H264" s="3" t="n">
@@ -11416,13 +11997,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E265" s="7" t="n">
+      <c r="E265" s="4" t="n">
         <v>1677</v>
       </c>
-      <c r="F265" s="4" t="n">
+      <c r="F265" s="5" t="n">
         <v>3.019749147584973</v>
       </c>
-      <c r="G265" s="8" t="n">
+      <c r="G265" s="9" t="n">
         <v>0.5307096004770423</v>
       </c>
       <c r="H265" s="3" t="n">
@@ -11448,13 +12029,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E266" s="7" t="n">
+      <c r="E266" s="4" t="n">
         <v>10279</v>
       </c>
-      <c r="F266" s="4" t="n">
+      <c r="F266" s="5" t="n">
         <v>2.973518380474754</v>
       </c>
-      <c r="G266" s="8" t="n">
+      <c r="G266" s="9" t="n">
         <v>0.5070532152933165</v>
       </c>
       <c r="H266" s="3" t="n">
@@ -11480,13 +12061,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E267" s="7" t="n">
+      <c r="E267" s="4" t="n">
         <v>14431</v>
       </c>
-      <c r="F267" s="4" t="n">
+      <c r="F267" s="5" t="n">
         <v>2.961829238167833</v>
       </c>
-      <c r="G267" s="8" t="n">
+      <c r="G267" s="9" t="n">
         <v>0.4667036241424711</v>
       </c>
       <c r="H267" s="3" t="n">
@@ -11512,13 +12093,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E268" s="7" t="n">
+      <c r="E268" s="4" t="n">
         <v>2202</v>
       </c>
-      <c r="F268" s="4" t="n">
+      <c r="F268" s="5" t="n">
         <v>2.95636765808356</v>
       </c>
-      <c r="G268" s="8" t="n">
+      <c r="G268" s="9" t="n">
         <v>0.5059037238873751</v>
       </c>
       <c r="H268" s="3" t="n">
@@ -11544,13 +12125,13 @@
           <t>Dopa</t>
         </is>
       </c>
-      <c r="E269" s="7" t="n">
+      <c r="E269" s="4" t="n">
         <v>1976</v>
       </c>
-      <c r="F269" s="4" t="n">
+      <c r="F269" s="5" t="n">
         <v>2.953504173987854</v>
       </c>
-      <c r="G269" s="8" t="n">
+      <c r="G269" s="9" t="n">
         <v>0.4701417004048583</v>
       </c>
       <c r="H269" s="3" t="n">
@@ -11576,13 +12157,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E270" s="7" t="n">
+      <c r="E270" s="4" t="n">
         <v>7810</v>
       </c>
-      <c r="F270" s="4" t="n">
+      <c r="F270" s="5" t="n">
         <v>2.917082774263764</v>
       </c>
-      <c r="G270" s="8" t="n">
+      <c r="G270" s="9" t="n">
         <v>0.5076824583866837</v>
       </c>
       <c r="H270" s="3" t="n">
@@ -11608,13 +12189,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E271" s="7" t="n">
+      <c r="E271" s="4" t="n">
         <v>36320</v>
       </c>
-      <c r="F271" s="4" t="n">
+      <c r="F271" s="5" t="n">
         <v>2.882052247948789</v>
       </c>
-      <c r="G271" s="8" t="n">
+      <c r="G271" s="9" t="n">
         <v>0.4995319383259912</v>
       </c>
       <c r="H271" s="3" t="n">
@@ -11640,13 +12221,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E272" s="7" t="n">
+      <c r="E272" s="4" t="n">
         <v>9491</v>
       </c>
-      <c r="F272" s="4" t="n">
+      <c r="F272" s="5" t="n">
         <v>2.878147945664314</v>
       </c>
-      <c r="G272" s="8" t="n">
+      <c r="G272" s="9" t="n">
         <v>0.5537877989674428</v>
       </c>
       <c r="H272" s="3" t="n">
@@ -11668,13 +12249,13 @@
         </is>
       </c>
       <c r="D273" s="3" t="n"/>
-      <c r="E273" s="7" t="n">
+      <c r="E273" s="4" t="n">
         <v>23170</v>
       </c>
-      <c r="F273" s="4" t="n">
+      <c r="F273" s="5" t="n">
         <v>2.85009551456625</v>
       </c>
-      <c r="G273" s="8" t="n">
+      <c r="G273" s="9" t="n">
         <v>0.3519205869659041</v>
       </c>
       <c r="H273" s="3" t="n">
@@ -11700,13 +12281,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E274" s="7" t="n">
+      <c r="E274" s="4" t="n">
         <v>1081</v>
       </c>
-      <c r="F274" s="4" t="n">
+      <c r="F274" s="5" t="n">
         <v>2.8474310839963</v>
       </c>
-      <c r="G274" s="8" t="n">
+      <c r="G274" s="9" t="n">
         <v>0.4921369102682701</v>
       </c>
       <c r="H274" s="3" t="n">
@@ -11732,13 +12313,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E275" s="7" t="n">
+      <c r="E275" s="4" t="n">
         <v>4339</v>
       </c>
-      <c r="F275" s="4" t="n">
+      <c r="F275" s="5" t="n">
         <v>2.820172443558423</v>
       </c>
-      <c r="G275" s="8" t="n">
+      <c r="G275" s="9" t="n">
         <v>0.460244295920719</v>
       </c>
       <c r="H275" s="3" t="n">
@@ -11764,13 +12345,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E276" s="7" t="n">
+      <c r="E276" s="4" t="n">
         <v>13098</v>
       </c>
-      <c r="F276" s="4" t="n">
+      <c r="F276" s="5" t="n">
         <v>2.766941243579172</v>
       </c>
-      <c r="G276" s="8" t="n">
+      <c r="G276" s="9" t="n">
         <v>0.4253321117727897</v>
       </c>
       <c r="H276" s="3" t="n">
@@ -11796,13 +12377,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E277" s="7" t="n">
+      <c r="E277" s="4" t="n">
         <v>1563</v>
       </c>
-      <c r="F277" s="4" t="n">
+      <c r="F277" s="5" t="n">
         <v>2.689862134357006</v>
       </c>
-      <c r="G277" s="8" t="n">
+      <c r="G277" s="9" t="n">
         <v>0.5630198336532309</v>
       </c>
       <c r="H277" s="3" t="n">
@@ -11828,13 +12409,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E278" s="7" t="n">
+      <c r="E278" s="4" t="n">
         <v>14101</v>
       </c>
-      <c r="F278" s="4" t="n">
+      <c r="F278" s="5" t="n">
         <v>2.675814102957237</v>
       </c>
-      <c r="G278" s="8" t="n">
+      <c r="G278" s="9" t="n">
         <v>0.4682646620807035</v>
       </c>
       <c r="H278" s="3" t="n">
@@ -11860,13 +12441,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E279" s="7" t="n">
+      <c r="E279" s="4" t="n">
         <v>83060</v>
       </c>
-      <c r="F279" s="4" t="n">
+      <c r="F279" s="5" t="n">
         <v>2.661670347065976</v>
       </c>
-      <c r="G279" s="8" t="n">
+      <c r="G279" s="9" t="n">
         <v>0.4742114134360703</v>
       </c>
       <c r="H279" s="3" t="n">
@@ -11892,13 +12473,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E280" s="7" t="n">
+      <c r="E280" s="4" t="n">
         <v>3440</v>
       </c>
-      <c r="F280" s="4" t="n">
+      <c r="F280" s="5" t="n">
         <v>2.637887452093024</v>
       </c>
-      <c r="G280" s="8" t="n">
+      <c r="G280" s="9" t="n">
         <v>0.4799418604651163</v>
       </c>
       <c r="H280" s="3" t="n">
@@ -11924,13 +12505,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E281" s="7" t="n">
+      <c r="E281" s="4" t="n">
         <v>2320</v>
       </c>
-      <c r="F281" s="4" t="n">
+      <c r="F281" s="5" t="n">
         <v>2.608982849741379</v>
       </c>
-      <c r="G281" s="8" t="n">
+      <c r="G281" s="9" t="n">
         <v>0.4870689655172414</v>
       </c>
       <c r="H281" s="3" t="n">
@@ -11956,13 +12537,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E282" s="7" t="n">
+      <c r="E282" s="4" t="n">
         <v>10331</v>
       </c>
-      <c r="F282" s="4" t="n">
+      <c r="F282" s="5" t="n">
         <v>2.608701013319137</v>
       </c>
-      <c r="G282" s="8" t="n">
+      <c r="G282" s="9" t="n">
         <v>0.494434227083535</v>
       </c>
       <c r="H282" s="3" t="n">
@@ -11988,13 +12569,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E283" s="7" t="n">
+      <c r="E283" s="4" t="n">
         <v>24710</v>
       </c>
-      <c r="F283" s="4" t="n">
+      <c r="F283" s="5" t="n">
         <v>2.587986873302307</v>
       </c>
-      <c r="G283" s="8" t="n">
+      <c r="G283" s="9" t="n">
         <v>0.478470254957507</v>
       </c>
       <c r="H283" s="3" t="n">
@@ -12020,13 +12601,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E284" s="7" t="n">
+      <c r="E284" s="4" t="n">
         <v>6585</v>
       </c>
-      <c r="F284" s="4" t="n">
+      <c r="F284" s="5" t="n">
         <v>2.556578436142749</v>
       </c>
-      <c r="G284" s="8" t="n">
+      <c r="G284" s="9" t="n">
         <v>0.455125284738041</v>
       </c>
       <c r="H284" s="3" t="n">
@@ -12052,13 +12633,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E285" s="7" t="n">
+      <c r="E285" s="4" t="n">
         <v>682</v>
       </c>
-      <c r="F285" s="4" t="n">
+      <c r="F285" s="5" t="n">
         <v>2.554698430058651</v>
       </c>
-      <c r="G285" s="8" t="n">
+      <c r="G285" s="9" t="n">
         <v>0.4662756598240469</v>
       </c>
       <c r="H285" s="3" t="n">
@@ -12084,13 +12665,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E286" s="7" t="n">
+      <c r="E286" s="4" t="n">
         <v>1704</v>
       </c>
-      <c r="F286" s="4" t="n">
+      <c r="F286" s="5" t="n">
         <v>2.544456881161972</v>
       </c>
-      <c r="G286" s="8" t="n">
+      <c r="G286" s="9" t="n">
         <v>0.4964788732394365</v>
       </c>
       <c r="H286" s="3" t="n">
@@ -12116,13 +12697,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E287" s="7" t="n">
+      <c r="E287" s="4" t="n">
         <v>14294</v>
       </c>
-      <c r="F287" s="4" t="n">
+      <c r="F287" s="5" t="n">
         <v>2.531913066489436</v>
       </c>
-      <c r="G287" s="8" t="n">
+      <c r="G287" s="9" t="n">
         <v>0.4352875332307261</v>
       </c>
       <c r="H287" s="3" t="n">
@@ -12148,13 +12729,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E288" s="7" t="n">
+      <c r="E288" s="4" t="n">
         <v>49319</v>
       </c>
-      <c r="F288" s="4" t="n">
+      <c r="F288" s="5" t="n">
         <v>2.489708781867029</v>
       </c>
-      <c r="G288" s="8" t="n">
+      <c r="G288" s="9" t="n">
         <v>0.4662706056489385</v>
       </c>
       <c r="H288" s="3" t="n">
@@ -12180,13 +12761,13 @@
           <t>Glut</t>
         </is>
       </c>
-      <c r="E289" s="7" t="n">
+      <c r="E289" s="4" t="n">
         <v>1832</v>
       </c>
-      <c r="F289" s="4" t="n">
+      <c r="F289" s="5" t="n">
         <v>2.360804431823144</v>
       </c>
-      <c r="G289" s="8" t="n">
+      <c r="G289" s="9" t="n">
         <v>0.3367903930131004</v>
       </c>
       <c r="H289" s="3" t="n">
@@ -12212,13 +12793,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E290" s="7" t="n">
+      <c r="E290" s="4" t="n">
         <v>2509</v>
       </c>
-      <c r="F290" s="4" t="n">
+      <c r="F290" s="5" t="n">
         <v>2.292973779075329</v>
       </c>
-      <c r="G290" s="8" t="n">
+      <c r="G290" s="9" t="n">
         <v>0.3882024711040255</v>
       </c>
       <c r="H290" s="3" t="n">
@@ -12244,13 +12825,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E291" s="7" t="n">
+      <c r="E291" s="4" t="n">
         <v>16700</v>
       </c>
-      <c r="F291" s="4" t="n">
+      <c r="F291" s="5" t="n">
         <v>2.217751568167665</v>
       </c>
-      <c r="G291" s="8" t="n">
+      <c r="G291" s="9" t="n">
         <v>0.3680239520958083</v>
       </c>
       <c r="H291" s="3" t="n">
@@ -12276,13 +12857,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E292" s="7" t="n">
+      <c r="E292" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="F292" s="4" t="n">
+      <c r="F292" s="5" t="n">
         <v>2.2115512836</v>
       </c>
-      <c r="G292" s="8" t="n">
+      <c r="G292" s="9" t="n">
         <v>0.322</v>
       </c>
       <c r="H292" s="3" t="n">
@@ -12308,13 +12889,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E293" s="7" t="n">
+      <c r="E293" s="4" t="n">
         <v>1100</v>
       </c>
-      <c r="F293" s="4" t="n">
+      <c r="F293" s="5" t="n">
         <v>2.148091536363636</v>
       </c>
-      <c r="G293" s="8" t="n">
+      <c r="G293" s="9" t="n">
         <v>0.3518181818181818</v>
       </c>
       <c r="H293" s="3" t="n">
@@ -12340,13 +12921,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E294" s="7" t="n">
+      <c r="E294" s="4" t="n">
         <v>4595</v>
       </c>
-      <c r="F294" s="4" t="n">
+      <c r="F294" s="5" t="n">
         <v>1.978274600239391</v>
       </c>
-      <c r="G294" s="8" t="n">
+      <c r="G294" s="9" t="n">
         <v>0.3862894450489662</v>
       </c>
       <c r="H294" s="3" t="n">
@@ -12372,13 +12953,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E295" s="7" t="n">
+      <c r="E295" s="4" t="n">
         <v>33543</v>
       </c>
-      <c r="F295" s="4" t="n">
+      <c r="F295" s="5" t="n">
         <v>1.267535100730406</v>
       </c>
-      <c r="G295" s="8" t="n">
+      <c r="G295" s="9" t="n">
         <v>0.1935426169394508</v>
       </c>
       <c r="H295" s="3" t="n">
@@ -12400,13 +12981,13 @@
         </is>
       </c>
       <c r="D296" s="3" t="n"/>
-      <c r="E296" s="7" t="n">
+      <c r="E296" s="4" t="n">
         <v>7857</v>
       </c>
-      <c r="F296" s="4" t="n">
+      <c r="F296" s="5" t="n">
         <v>1.203411173657884</v>
       </c>
-      <c r="G296" s="8" t="n">
+      <c r="G296" s="9" t="n">
         <v>0.1743668066692121</v>
       </c>
       <c r="H296" s="3" t="n">
@@ -12432,13 +13013,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E297" s="7" t="n">
+      <c r="E297" s="4" t="n">
         <v>4566</v>
       </c>
-      <c r="F297" s="4" t="n">
+      <c r="F297" s="5" t="n">
         <v>0.7941136664323259</v>
       </c>
-      <c r="G297" s="8" t="n">
+      <c r="G297" s="9" t="n">
         <v>0.1127901883486639</v>
       </c>
       <c r="H297" s="3" t="n">
@@ -12464,13 +13045,13 @@
           <t>GABA</t>
         </is>
       </c>
-      <c r="E298" s="7" t="n">
+      <c r="E298" s="4" t="n">
         <v>2243</v>
       </c>
-      <c r="F298" s="4" t="n">
+      <c r="F298" s="5" t="n">
         <v>0.656512470708872</v>
       </c>
-      <c r="G298" s="8" t="n">
+      <c r="G298" s="9" t="n">
         <v>0.09451627284886301</v>
       </c>
       <c r="H298" s="3" t="n">
@@ -12482,7 +13063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12505,34 +13086,34 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tespit orani ile ifade seviyesinin ayrilmasi</t>
+          <t>Tespit oranı ile ifade seviyesinin ayrılması</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Genel sira</t>
+          <t>Genel sıra</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ortalama (log2, sifirlar dahil)</t>
+          <t>Ortalama (log2, sıfırlar dahil)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tespit orani</t>
+          <t>Tespit oranı</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -12542,17 +13123,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Yaniltici kat</t>
+          <t>Yanıltıcı kat</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tespit orani kati</t>
+          <t>Tespit oranı katı</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Seviye kati</t>
+          <t>Seviye katı</t>
         </is>
       </c>
     </row>
@@ -12565,25 +13146,25 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="4" t="n">
         <v>371211</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>7.765019914220215</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <v>0.9250264674268812</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="4" t="n">
         <v>335.4797636443221</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12596,25 +13177,25 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="4" t="n">
         <v>106459</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>6.764457360101072</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>0.850797020449187</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="4" t="n">
         <v>246.4048478492157</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>2.000780017670547</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="6" t="n">
         <v>1.087246952203129</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="6" t="n">
         <v>1.361498227703761</v>
       </c>
     </row>
@@ -12627,25 +13208,25 @@
       <c r="B5" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="4" t="n">
         <v>13705</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>4.424467163531558</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>0.569500182415177</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="4" t="n">
         <v>217.1286634284079</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>10.12993316644151</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="6" t="n">
         <v>1.624277736846304</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="6" t="n">
         <v>1.545073590686644</v>
       </c>
     </row>
@@ -12658,25 +13239,25 @@
       <c r="B6" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="4" t="n">
         <v>5516</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>4.139340412146483</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>0.5398839738941261</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="4" t="n">
         <v>202.2473290800229</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>12.34349895999417</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="6" t="n">
         <v>1.713380118981423</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="6" t="n">
         <v>1.658759921183351</v>
       </c>
     </row>
@@ -12689,25 +13270,25 @@
       <c r="B7" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="4" t="n">
         <v>139030</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>4.086697386960369</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>0.5374955045673596</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="4" t="n">
         <v>193.4454302475901</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>12.80222378399456</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="6" t="n">
         <v>1.720993867979329</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="6" t="n">
         <v>1.734234627382734</v>
       </c>
     </row>
@@ -12720,25 +13301,25 @@
       <c r="B8" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="4" t="n">
         <v>81472</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>3.879017706744648</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>0.4917272191673212</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="4" t="n">
         <v>235.9692420590459</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>14.78438378079829</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="6" t="n">
         <v>1.88117808282669</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="6" t="n">
         <v>1.421709714015931</v>
       </c>
     </row>
@@ -12751,25 +13332,25 @@
       <c r="B9" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="4" t="n">
         <v>84356</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>3.790201947700223</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>0.4937763763099246</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="4" t="n">
         <v>203.4987653894541</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>15.72314556804754</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="6" t="n">
         <v>1.873371250240366</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="6" t="n">
         <v>1.648559208712073</v>
       </c>
     </row>
@@ -12782,25 +13363,25 @@
       <c r="B10" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="4" t="n">
         <v>144668</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>3.772723433937706</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="9" t="n">
         <v>0.5096496806481047</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="4" t="n">
         <v>168.1995320023066</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>15.9147929238524</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="6" t="n">
         <v>1.815024128437706</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="6" t="n">
         <v>1.994534465409342</v>
       </c>
     </row>
@@ -12813,25 +13394,25 @@
       <c r="B11" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="4" t="n">
         <v>3321</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>3.606476154080097</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>0.5323697681421259</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="4" t="n">
         <v>108.4692575159436</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>17.85855888344941</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="6" t="n">
         <v>1.73756385651848</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="6" t="n">
         <v>3.09285572084801</v>
       </c>
     </row>
@@ -12844,25 +13425,25 @@
       <c r="B12" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="4" t="n">
         <v>8544</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>3.433970357876873</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <v>0.4590355805243445</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="4" t="n">
         <v>177.6307951743404</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>20.12685089160359</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="6" t="n">
         <v>2.015151998392472</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="6" t="n">
         <v>1.888635150876044</v>
       </c>
     </row>
@@ -12875,25 +13456,25 @@
       <c r="B13" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="4" t="n">
         <v>23170</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>2.85009551456625</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>0.3519205869659041</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="4" t="n">
         <v>273.1248607492214</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>30.1675242643276</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="6" t="n">
         <v>2.628509105994707</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="6" t="n">
         <v>1.228301820361765</v>
       </c>
     </row>
@@ -12902,7 +13483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12927,7 +13508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ozellik</t>
+          <t>Özellik</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -12937,7 +13518,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yaslanma kohortu</t>
+          <t>Yaşlanma kohortu</t>
         </is>
       </c>
     </row>
@@ -12961,7 +13542,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Hucre sayisi</t>
+          <t>Hücre sayısı</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -12978,41 +13559,41 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Parca / bolge</t>
+          <t>Parça / bölge</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>13 parca</t>
+          <t>13 parça</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>7 anatomik bolge</t>
+          <t>7 anatomik bölge</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Fare sayisi</t>
+          <t>Fare sayısı</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>cikarilmadi</t>
+          <t>çıkarılmadı</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>108 (64 genc, 44 yasli)</t>
+          <t>108 (64 genç, 44 yaşlı)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Gen sayisi</t>
+          <t>Gen sayısı</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -13029,24 +13610,24 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Ifade matrisi (disk)</t>
+          <t>İfade matrisi (disk)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>yaklasik 95 GB</t>
+          <t>yaklaşık 95 GB</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>yaklasik 13 GB</t>
+          <t>yaklaşık 13 GB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Yontem</t>
+          <t>Yöntem</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -13063,7 +13644,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Deger birimi</t>
+          <t>Değer birimi</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -13080,7 +13661,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Metadata surumu</t>
+          <t>Metadata sürümü</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -13098,29 +13679,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Parcalara gore hucre dagilimi</t>
+          <t>Parçalara göre hücre dağılımı</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Parca</t>
+          <t>Parça</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Hucre</t>
+          <t>Hücre</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Alt sinif</t>
+          <t>Alt sınıf</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Yuzde</t>
+          <t>Yüzde</t>
         </is>
       </c>
     </row>
@@ -13130,13 +13711,13 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="4" t="n">
         <v>337101</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="9" t="n">
         <v>0.1439771926452688</v>
       </c>
     </row>
@@ -13146,13 +13727,13 @@
           <t>STR</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="4" t="n">
         <v>283782</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <v>0.1212044333397399</v>
       </c>
     </row>
@@ -13162,13 +13743,13 @@
           <t>Isocortex-1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="4" t="n">
         <v>227670</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="9" t="n">
         <v>0.09723877250304312</v>
       </c>
     </row>
@@ -13178,13 +13759,13 @@
           <t>Isocortex-2</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="4" t="n">
         <v>227537</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="9" t="n">
         <v>0.09718196766822559</v>
       </c>
     </row>
@@ -13194,13 +13775,13 @@
           <t>MY</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="4" t="n">
         <v>191746</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>0.08189548764601619</v>
       </c>
     </row>
@@ -13210,13 +13791,13 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="4" t="n">
         <v>181723</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <v>0.07761462404168536</v>
       </c>
     </row>
@@ -13226,13 +13807,13 @@
           <t>HPF</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="4" t="n">
         <v>181055</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <v>0.0773293185555342</v>
       </c>
     </row>
@@ -13242,13 +13823,13 @@
           <t>HY</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="4" t="n">
         <v>162296</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="9" t="n">
         <v>0.06931727422213681</v>
       </c>
     </row>
@@ -13258,13 +13839,13 @@
           <t>P</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="4" t="n">
         <v>143157</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <v>0.06114293036068934</v>
       </c>
     </row>
@@ -13274,13 +13855,13 @@
           <t>TH</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="4" t="n">
         <v>130454</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="9" t="n">
         <v>0.05571742797958443</v>
       </c>
     </row>
@@ -13290,13 +13871,13 @@
           <t>PAL</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="4" t="n">
         <v>108046</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>0.0461468810728853</v>
       </c>
     </row>
@@ -13306,13 +13887,13 @@
           <t>OLF</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="4" t="n">
         <v>88560</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="9" t="n">
         <v>0.03782433211608687</v>
       </c>
     </row>
@@ -13322,13 +13903,13 @@
           <t>CTXsp</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="4" t="n">
         <v>78223</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="9" t="n">
         <v>0.03340935784910415</v>
       </c>
     </row>
@@ -13343,62 +13924,62 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Duzey</t>
+          <t>Düzey</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Sayi</t>
+          <t>Sayı</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Sinif (class)</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
+          <t>Sınıf (class)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Alt sinif (subclass)</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
+          <t>Alt sınıf (subclass)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
         <v>338</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Supertip (supertype)</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
+          <t>Süpertip (supertype)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
         <v>1201</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Kume (cluster)</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
+          <t>Küme (cluster)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
         <v>5322</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Notrotransmitter tipi</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
+          <t>Nörotransmitter tipi</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
         <v>10</v>
       </c>
     </row>
